--- a/noprofit/en/11255/inpas-template.xlsx
+++ b/noprofit/en/11255/inpas-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA20E27-1C79-401B-9F4F-65F1E594FB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C27F2B-9ECA-48EA-98F6-1411ACF05CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Notes of Financial Statement" sheetId="4" r:id="rId6"/>
     <sheet name="Notes of Income Statement" sheetId="10" r:id="rId7"/>
     <sheet name="Notes of Cash flows statement" sheetId="9" r:id="rId8"/>
+    <sheet name="Additional INPAS Notes" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash Flows Statement - indirect'!$A$1:$E$56</definedName>
@@ -31,7 +32,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Statement of Changes NetAssets'!$A$1:$E$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Statement of Financial Position'!$A$1:$E$50</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="349">
   <si>
     <t>Company name and legal form</t>
   </si>
@@ -243,12 +244,6 @@
     <t>Payables</t>
   </si>
   <si>
-    <t>Deferred Rev Liability</t>
-  </si>
-  <si>
-    <t>Liability for deferred revenue (income with restrictions)</t>
-  </si>
-  <si>
     <t>Interest Payable</t>
   </si>
   <si>
@@ -366,30 +361,18 @@
     <t>Investment Property</t>
   </si>
   <si>
-    <t>NET PROFIT OR LOSS</t>
-  </si>
-  <si>
     <t>EQB</t>
   </si>
   <si>
     <t>Code</t>
   </si>
   <si>
-    <t>Comprehensive income</t>
-  </si>
-  <si>
     <t>PLE</t>
   </si>
   <si>
     <t>OCI</t>
   </si>
   <si>
-    <t>[+] Other comprehensive income</t>
-  </si>
-  <si>
-    <t>Total comprehensive income</t>
-  </si>
-  <si>
     <t>EQE</t>
   </si>
   <si>
@@ -414,18 +397,12 @@
     <t>Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
   </si>
   <si>
-    <t>Net increase (decrease) in cash and cash equivalents</t>
-  </si>
-  <si>
     <t>Cash and cash equivalents at beginning of period</t>
   </si>
   <si>
     <t>Cash and cash equivalents at end of period</t>
   </si>
   <si>
-    <t>Change in Cash and Cash Equivalents</t>
-  </si>
-  <si>
     <t>Others notes</t>
   </si>
   <si>
@@ -435,12 +412,6 @@
     <t>Description of acquisition of assets by assuming directly related liabilities or means of finance lease</t>
   </si>
   <si>
-    <t xml:space="preserve">Description of acquisition of entity by means of equity issue </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description of conversion of debt to equity </t>
-  </si>
-  <si>
     <t>Commentary by management on significant cash and cash equivalent balances held by entity that are not available for use by group</t>
   </si>
   <si>
@@ -543,18 +514,9 @@
     <t>Total expenses</t>
   </si>
   <si>
-    <t>Total Explanation of investing and financing transactions not requiring use of cash or cash equivalents</t>
-  </si>
-  <si>
-    <t>Total Description of acquisition of assets by assuming directly related liabilities or means of finance lease</t>
-  </si>
-  <si>
     <t>Total Commentary by management on significant cash and cash equivalent balances held by entity that are not available for use by group</t>
   </si>
   <si>
-    <t>Total Surplus or deficit from operating activities</t>
-  </si>
-  <si>
     <t>Profit or Loss</t>
   </si>
   <si>
@@ -648,9 +610,6 @@
     <t>Opening cash and cash equivalents</t>
   </si>
   <si>
-    <t>Movement if cash and cash equivalents</t>
-  </si>
-  <si>
     <t>Foreign exchange differences</t>
   </si>
   <si>
@@ -795,12 +754,6 @@
     <t>[+/-] Increase/decrease in accruals</t>
   </si>
   <si>
-    <t>[-] Capital grant</t>
-  </si>
-  <si>
-    <t>[+] Receipt of grants for PPE</t>
-  </si>
-  <si>
     <t>[-] Repayment of borrowings</t>
   </si>
   <si>
@@ -810,30 +763,18 @@
     <t>[+] Member shares issued</t>
   </si>
   <si>
-    <t>[+]  Donations of property, plant and equipment (PPE)</t>
-  </si>
-  <si>
     <t>[-] Acquisition of PPE</t>
   </si>
   <si>
     <t>[-] Acquisition of intangible assets</t>
   </si>
   <si>
-    <t>[-] Disposals</t>
-  </si>
-  <si>
     <t>Statement of Changes in Net Assets</t>
   </si>
   <si>
     <t>Net Assets at beginning of period</t>
   </si>
   <si>
-    <t>Increase (decrease) in Net Assets</t>
-  </si>
-  <si>
-    <t>Total increase (decrease) in Net Assets</t>
-  </si>
-  <si>
     <t>Net Assets at end of period</t>
   </si>
   <si>
@@ -843,12 +784,6 @@
     <t>Description of conversion of debt to net assets</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Description of acquisition of entity by means of net assets issue </t>
-  </si>
-  <si>
-    <t>Total Description of conversion of debt to net assets</t>
-  </si>
-  <si>
     <t>Notes to the Statement of Cash Flows</t>
   </si>
   <si>
@@ -874,6 +809,297 @@
   </si>
   <si>
     <t>Description of nature of entity's operation and activities (Activity A, B, C, D)</t>
+  </si>
+  <si>
+    <t>Grant oblig. liability</t>
+  </si>
+  <si>
+    <t>Liabilities for unfulfilled grant delivery obligations</t>
+  </si>
+  <si>
+    <t>Total other gains and losses</t>
+  </si>
+  <si>
+    <t>TOTAL SURPLUS OR DEFICIT</t>
+  </si>
+  <si>
+    <t>Surplus and movements recognised directly in net assets</t>
+  </si>
+  <si>
+    <t>Gains and losses recognised directly in net assets</t>
+  </si>
+  <si>
+    <t>Total surplus and direct net asset movements</t>
+  </si>
+  <si>
+    <t>Other movements in net assets (excluding surplus)</t>
+  </si>
+  <si>
+    <t>Total other movements in net assets</t>
+  </si>
+  <si>
+    <t>[+] Depreciation and amortisation expenses</t>
+  </si>
+  <si>
+    <t>[+] Impairment expenses</t>
+  </si>
+  <si>
+    <t>[-] Donations of PPE received in kind (non-cash)</t>
+  </si>
+  <si>
+    <t>[-/+] Unrealised foreign exchange gains/losses</t>
+  </si>
+  <si>
+    <t>[-/+] Gain/loss on asset disposals (non-cash reversal)</t>
+  </si>
+  <si>
+    <t>[+/-] Capital grant accrual adjustments</t>
+  </si>
+  <si>
+    <t>[+/-] Other investing cash flows</t>
+  </si>
+  <si>
+    <t>[+] Receipts from disposal of assets</t>
+  </si>
+  <si>
+    <t>Movement in cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Closing cash and cash equivalents (calculated)</t>
+  </si>
+  <si>
+    <t>Reconciliation difference (must equal zero)</t>
+  </si>
+  <si>
+    <t>Other gains and losses</t>
+  </si>
+  <si>
+    <t>Cash and cash equivalents reconciliation</t>
+  </si>
+  <si>
+    <t>Cash movement before exchange effects</t>
+  </si>
+  <si>
+    <t>Closing cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Total non-cash investing and financing transactions</t>
+  </si>
+  <si>
+    <t>Total non-cash asset acquisitions through liabilities or leases</t>
+  </si>
+  <si>
+    <t>Acquisition of entity through issue of equity claims</t>
+  </si>
+  <si>
+    <t>Total acquisition of entity through equity claims</t>
+  </si>
+  <si>
+    <t>Conversion of debt to equity claims</t>
+  </si>
+  <si>
+    <t>Total conversion of debt to equity claims</t>
+  </si>
+  <si>
+    <t>ADDITIONAL EXPLANATORY NOTES | INPAS 2025</t>
+  </si>
+  <si>
+    <t>Complete the yellow cells below. Explain only material matters that apply to your organisation; use amounts or references from Banana Accounting where available.</t>
+  </si>
+  <si>
+    <t>This sheet complements the three existing numerical notes sheets. Prior-year figures and fund movement reports can be supplied directly by your accounting software; do not duplicate them here.</t>
+  </si>
+  <si>
+    <t>Reporting organisation</t>
+  </si>
+  <si>
+    <t>B1.10</t>
+  </si>
+  <si>
+    <t>Reporting dates (start / end)</t>
+  </si>
+  <si>
+    <t>Presentation currency</t>
+  </si>
+  <si>
+    <t>Rounding applied (units / thousands, etc.)</t>
+  </si>
+  <si>
+    <t>Important: do not enter an unrestricted INPAS compliance claim unless the entire applicable Standard has been followed. If first-time adoption applies, use the appropriate transition disclosure.</t>
+  </si>
+  <si>
+    <t>1. PREPARATION AND ACCOUNTING POLICIES</t>
+  </si>
+  <si>
+    <t>TOPIC</t>
+  </si>
+  <si>
+    <t>WHAT SHOULD BE EXPLAINED</t>
+  </si>
+  <si>
+    <t>WRITE YOUR NOTE OR REFER TO A REPORT</t>
+  </si>
+  <si>
+    <t>INPAS</t>
+  </si>
+  <si>
+    <t>Basis and level of INPAS compliance</t>
+  </si>
+  <si>
+    <t>State the reporting basis and whether full INPAS compliance, financial-statements-only transition compliance, or neither is claimed. Only make a compliance statement if all relevant conditions are fulfilled.</t>
+  </si>
+  <si>
+    <t>B1.3, B1.20; Z1.5</t>
+  </si>
+  <si>
+    <t>Material accounting policies</t>
+  </si>
+  <si>
+    <t>Explain the policies important to your figures: when income and expenses are recognised (accrual), valuation, depreciation, foreign-currency treatment, and other relevant methods. Do not repeat immaterial policies.</t>
+  </si>
+  <si>
+    <t>B6.2, B6.5</t>
+  </si>
+  <si>
+    <t>Significant judgements and estimates</t>
+  </si>
+  <si>
+    <t>Describe judgements with a major accounting effect and important estimates that could materially change asset or liability values next year. Give relevant amounts or refer to the accounting report.</t>
+  </si>
+  <si>
+    <t>B6.6-B6.7</t>
+  </si>
+  <si>
+    <t>Going concern - if uncertain</t>
+  </si>
+  <si>
+    <t>Describe major uncertainties about the ability to continue activities. If the accounts are not prepared on a going-concern basis, explain why and what basis was used.</t>
+  </si>
+  <si>
+    <t>B1.4-B1.5</t>
+  </si>
+  <si>
+    <t>First-time adoption - if relevant</t>
+  </si>
+  <si>
+    <t>In the first INPAS report, explain the transition, material accounting policy changes and the required reconciliations; refer to the transition schedules prepared from the accounting software.</t>
+  </si>
+  <si>
+    <t>Z1.3-Z1.18</t>
+  </si>
+  <si>
+    <t>2. GRANTS, DONATIONS AND FUNDS</t>
+  </si>
+  <si>
+    <t>Grants and donation revenue analysis</t>
+  </si>
+  <si>
+    <t>Disclose revenue WITH and WITHOUT delivery obligations. For each group show how much is cash, donated goods and donated services. Enter amounts here or clearly cite the corresponding report.</t>
+  </si>
+  <si>
+    <t>C1.106</t>
+  </si>
+  <si>
+    <t>Income without delivery obligations</t>
+  </si>
+  <si>
+    <t>Describe when grants/donations become receivable and are recognised. Disclose opening and closing balances of related receivables unless already reported elsewhere.</t>
+  </si>
+  <si>
+    <t>C1.58-C1.60; C1.108</t>
+  </si>
+  <si>
+    <t>Grants WITH delivery obligations</t>
+  </si>
+  <si>
+    <t>Describe what must be delivered, timing, significant payment terms, how income is recognised, unfulfilled obligations where required, and opening/closing receivables and delivery-obligation assets/liabilities unless otherwise reported.</t>
+  </si>
+  <si>
+    <t>C1.110-C1.114</t>
+  </si>
+  <si>
+    <t>Donated goods and services</t>
+  </si>
+  <si>
+    <t>Explain donated goods or volunteer services not recognised when received, why they were not recognised, which permitted exception was used (if any), and their significance to the organisation.</t>
+  </si>
+  <si>
+    <t>C1.62-C1.68; C1.107</t>
+  </si>
+  <si>
+    <t>Explanation of individual funds</t>
+  </si>
+  <si>
+    <t>Refer to the detailed fund movement report from Banana Accounting. If that report does not include purposes of each fund, reasons for transfers, any restricted-fund shortfalls or plans for designated funds, explain them here.</t>
+  </si>
+  <si>
+    <t>B8.26-B8.27</t>
+  </si>
+  <si>
+    <t>3. EXPENSES AND OTHER RELEVANT DISCLOSURES</t>
+  </si>
+  <si>
+    <t>Expenses and cost allocation</t>
+  </si>
+  <si>
+    <t>If expenses are shown by function or in mixed categories, explain the choice, which expense types each function includes, and how shared costs are allocated. Disclose volunteer benefits and material unusual losses where relevant.</t>
+  </si>
+  <si>
+    <t>D1.12-D1.15</t>
+  </si>
+  <si>
+    <t>Assets, liabilities and other commitments</t>
+  </si>
+  <si>
+    <t>Describe significant asset valuations, depreciation/impairment, provisions, uncertain liabilities, financial-instrument risks, borrowing terms or leases that are applicable and not already detailed in existing notes.</t>
+  </si>
+  <si>
+    <t>E2, E5; D5-D6; F1</t>
+  </si>
+  <si>
+    <t>Related parties and governing body</t>
+  </si>
+  <si>
+    <t>Explain related-party transactions and outstanding balances (if any), key management remuneration, and whether governing-body members were paid benefits or compensation; state explicitly when none were paid.</t>
+  </si>
+  <si>
+    <t>H1.7-H1.14</t>
+  </si>
+  <si>
+    <t>Restricted or unavailable cash</t>
+  </si>
+  <si>
+    <t>If material bank/cash balances cannot be freely used, describe the amount and reason (such as donor restrictions). Refer to the existing Notes of Cash flows statement for the figures.</t>
+  </si>
+  <si>
+    <t>B5.25</t>
+  </si>
+  <si>
+    <t>Approval and events after year-end</t>
+  </si>
+  <si>
+    <t>State the date and person/body authorising the financial statements. If major events occurred afterwards but before authorisation, describe them and their estimated financial effect, if relevant.</t>
+  </si>
+  <si>
+    <t>H3.9-H3.10</t>
+  </si>
+  <si>
+    <t>Other relevant disclosures</t>
+  </si>
+  <si>
+    <t>Add any other material information required by the INPAS sections applicable to the organisation, not included in the accounting reports or other notes. In particular, explain unusual events or material policy changes.</t>
+  </si>
+  <si>
+    <t>B6.1-B6.3</t>
+  </si>
+  <si>
+    <t>HOW TO COMPLETE</t>
+  </si>
+  <si>
+    <t>Write an explanation or a reference to a specific accounting report in the yellow field. Where not applicable, mark N/A and omit that item from the published notes. Review all disclosures relevant to the actual transactions.</t>
+  </si>
+  <si>
+    <t>Source: INPAS 2025, The Standard (https://www.inprf.org). Paragraph references are shown on the right. This worksheet is a preparation aid; it is not, by itself, a statement of full INPAS compliance.</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1297,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1354,12 +1580,33 @@
     <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,18 +1616,6 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1405,47 +1640,54 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1836,333 +2078,327 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="A1" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="101">
+      <c r="B8" s="104">
         <v>45292</v>
       </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="101">
+      <c r="B9" s="104">
         <v>45657</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="101" t="s">
-        <v>273</v>
-      </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
+      <c r="B10" s="104" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="96"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="96"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="101"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="101" t="s">
+      <c r="B17" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="101"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="101"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
-      <c r="B19" s="101" t="s">
+      <c r="B19" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="101"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="101"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="101" t="s">
+      <c r="B21" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="101" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="101"/>
+      <c r="B22" s="104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" s="104"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
-      <c r="B23" s="101" t="s">
-        <v>268</v>
-      </c>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="101"/>
+      <c r="B23" s="104" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
-      <c r="B24" s="101" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="101"/>
+      <c r="B24" s="104" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
-      <c r="B25" s="101" t="s">
-        <v>270</v>
-      </c>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
+      <c r="B25" s="104" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
-      <c r="B26" s="101" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
+      <c r="B26" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
-      <c r="B27" s="101" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
+      <c r="B27" s="104" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
-      <c r="B28" s="101" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
+      <c r="B28" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2179,6 +2415,12 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2207,65 +2449,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="111" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="111" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="107" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="107"/>
@@ -2297,8 +2539,8 @@
         <v>27</v>
       </c>
       <c r="D9" s="74">
-        <f>$B$4</f>
-        <v>45292</v>
+        <f>$B$4-1</f>
+        <v>45291</v>
       </c>
       <c r="E9" s="74">
         <f>$B$5</f>
@@ -2345,6 +2587,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="14">
+        <f>'Notes of Financial Statement'!C48</f>
         <v>0</v>
       </c>
     </row>
@@ -2432,10 +2675,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C19" s="90">
         <v>6</v>
@@ -2529,8 +2772,8 @@
         <v>27</v>
       </c>
       <c r="D25" s="74">
-        <f>$B$4</f>
-        <v>45292</v>
+        <f>$B$4-1</f>
+        <v>45291</v>
       </c>
       <c r="E25" s="74">
         <f>$B$5</f>
@@ -2548,10 +2791,10 @@
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C27" s="90">
         <v>9</v>
@@ -2565,10 +2808,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C28" s="90">
         <v>10</v>
@@ -2582,10 +2825,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C29" s="90">
         <v>11</v>
@@ -2797,10 +3040,10 @@
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="C44" s="90">
         <v>20</v>
@@ -2814,10 +3057,10 @@
     </row>
     <row r="45" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C45" s="90">
         <v>21</v>
@@ -2831,10 +3074,10 @@
     </row>
     <row r="46" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" s="90">
         <v>22</v>
@@ -2848,10 +3091,10 @@
     </row>
     <row r="47" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C47" s="90">
         <v>23</v>
@@ -2865,10 +3108,10 @@
     </row>
     <row r="48" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C48" s="90">
         <v>24</v>
@@ -2883,7 +3126,7 @@
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
       <c r="B49" s="110" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C49" s="110"/>
       <c r="D49" s="62">
@@ -2898,7 +3141,7 @@
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="110" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C50" s="110"/>
       <c r="D50" s="62">
@@ -2926,10 +3169,10 @@
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="60" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B53" s="109" t="str">
-        <f>IF((D15+D23+D33=D39+D49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
+        <f>IF(ABS(D53)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
       <c r="C53" s="109"/>
@@ -2940,10 +3183,10 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="61" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B54" s="108" t="str">
-        <f>IF((E15+E23+E33=E39+E49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
+        <f>IF(ABS(E54)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
       <c r="C54" s="108"/>
@@ -2961,6 +3204,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B53:C53"/>
@@ -2971,11 +3219,6 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B53">
@@ -3029,13 +3272,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
@@ -3043,53 +3286,53 @@
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="112" t="str">
+      <c r="B2" s="115" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="112" t="str">
+      <c r="B3" s="115" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="116">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="116">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="107" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="107"/>
@@ -3115,14 +3358,14 @@
         <v>25</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="84">
-        <f>$B$4</f>
-        <v>45292</v>
+        <f>$B$4-1</f>
+        <v>45291</v>
       </c>
       <c r="E9" s="84">
         <f>$B$5</f>
@@ -3131,10 +3374,10 @@
     </row>
     <row r="10" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C10" s="91">
         <v>25</v>
@@ -3148,10 +3391,10 @@
     </row>
     <row r="11" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C11" s="91">
         <v>26</v>
@@ -3165,10 +3408,10 @@
     </row>
     <row r="12" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C12" s="91">
         <v>27</v>
@@ -3182,10 +3425,10 @@
     </row>
     <row r="13" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C13" s="91">
         <v>28</v>
@@ -3199,10 +3442,10 @@
     </row>
     <row r="14" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C14" s="91">
         <v>29</v>
@@ -3216,10 +3459,10 @@
     </row>
     <row r="15" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C15" s="91">
         <v>30</v>
@@ -3233,10 +3476,10 @@
     </row>
     <row r="16" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" s="91">
         <v>31</v>
@@ -3250,10 +3493,10 @@
     </row>
     <row r="17" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" s="91">
         <v>32</v>
@@ -3267,10 +3510,10 @@
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="91">
         <v>33</v>
@@ -3284,10 +3527,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" s="91">
         <v>34</v>
@@ -3302,7 +3545,7 @@
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47"/>
       <c r="B20" s="64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="64"/>
       <c r="D20" s="65">
@@ -3326,14 +3569,14 @@
         <v>25</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="84">
-        <f>$B$4</f>
-        <v>45292</v>
+        <f>$B$4-1</f>
+        <v>45291</v>
       </c>
       <c r="E22" s="84">
         <f>$B$5</f>
@@ -3342,10 +3585,10 @@
     </row>
     <row r="23" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C23" s="91">
         <v>35</v>
@@ -3359,10 +3602,10 @@
     </row>
     <row r="24" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C24" s="91">
         <v>36</v>
@@ -3376,10 +3619,10 @@
     </row>
     <row r="25" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C25" s="91">
         <v>37</v>
@@ -3393,10 +3636,10 @@
     </row>
     <row r="26" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C26" s="91">
         <v>38</v>
@@ -3410,10 +3653,10 @@
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" s="91">
         <v>39</v>
@@ -3427,10 +3670,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="91">
         <v>40</v>
@@ -3444,10 +3687,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="91">
         <v>41</v>
@@ -3461,10 +3704,10 @@
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" s="91">
         <v>42</v>
@@ -3479,7 +3722,7 @@
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="47"/>
       <c r="B31" s="64" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" s="64"/>
       <c r="D31" s="65">
@@ -3503,26 +3746,26 @@
         <v>25</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="84">
-        <f>$B$4</f>
-        <v>45292</v>
-      </c>
-      <c r="E33" s="84">
-        <f>$B$5</f>
-        <v>45657</v>
+      <c r="D33" s="103">
+        <f>SUM(D20,D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="103">
+        <f>SUM(E20,E31)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C34" s="91">
         <v>43</v>
@@ -3536,10 +3779,10 @@
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C35" s="91">
         <v>44</v>
@@ -3553,10 +3796,10 @@
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C36" s="91">
         <v>45</v>
@@ -3570,10 +3813,10 @@
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C37" s="91">
         <v>46</v>
@@ -3587,10 +3830,10 @@
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C38" s="91">
         <v>47</v>
@@ -3604,10 +3847,10 @@
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C39" s="91">
         <v>48</v>
@@ -3622,7 +3865,7 @@
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40" s="86" t="s">
-        <v>166</v>
+        <v>254</v>
       </c>
       <c r="C40" s="86"/>
       <c r="D40" s="87">
@@ -3637,15 +3880,15 @@
     <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="64" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="C41" s="64"/>
       <c r="D41" s="66">
-        <f>SUM(D20+D31+D40)</f>
+        <f>SUM(D33,D40)</f>
         <v>0</v>
       </c>
       <c r="E41" s="66">
-        <f>SUM(E20+E31+E40)</f>
+        <f>SUM(E33,E40)</f>
         <v>0</v>
       </c>
     </row>
@@ -3688,13 +3931,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3703,53 +3946,53 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="111" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="111" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="107" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="107"/>
@@ -3772,14 +4015,14 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="75"/>
       <c r="D9" s="74">
-        <f>DATE(YEAR(B5),1,1)</f>
+        <f>$B$4</f>
         <v>45292</v>
       </c>
       <c r="E9" s="74">
@@ -3789,13 +4032,14 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="114" t="s">
-        <v>257</v>
-      </c>
-      <c r="C10" s="114"/>
+        <v>102</v>
+      </c>
+      <c r="B10" s="117" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="117"/>
       <c r="D10" s="14">
+        <f>'Statement of Financial Position'!D33</f>
         <v>0</v>
       </c>
       <c r="E10" s="13"/>
@@ -3807,16 +4051,16 @@
       <c r="D11" s="53"/>
       <c r="E11" s="31"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="C12" s="75"/>
       <c r="D12" s="74">
-        <f>DATE(YEAR(B5),1,1)</f>
+        <f>$B$4</f>
         <v>45292</v>
       </c>
       <c r="E12" s="74">
@@ -3826,37 +4070,38 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="116" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
+        <v>104</v>
+      </c>
+      <c r="B13" s="119" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
       <c r="E13" s="14">
+        <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
+        <v>105</v>
+      </c>
+      <c r="B14" s="119" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
       <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
-      <c r="B15" s="115" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
+      <c r="B15" s="118" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
       <c r="E15" s="67">
         <f>SUM(E13:E14)</f>
         <v>0</v>
@@ -3869,16 +4114,16 @@
       <c r="D16" s="50"/>
       <c r="E16" s="51"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="76">
-        <f>DATE(YEAR(B4),1,1)</f>
+        <f>$B$4</f>
         <v>45292</v>
       </c>
       <c r="E17" s="74">
@@ -3888,76 +4133,76 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="117" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
+        <v>204</v>
+      </c>
+      <c r="B18" s="120" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
       <c r="E18" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="B19" s="117" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
+        <v>205</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
+        <v>206</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
       <c r="E20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21" s="117" t="s">
-        <v>239</v>
-      </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
+        <v>156</v>
+      </c>
+      <c r="B21" s="120" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
       <c r="E21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="116" t="s">
-        <v>240</v>
-      </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
+        <v>157</v>
+      </c>
+      <c r="B22" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
       <c r="E22" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
-      <c r="B23" s="115" t="s">
-        <v>259</v>
-      </c>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
+      <c r="B23" s="118" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
       <c r="E23" s="67">
         <f>SUM(E18:E22)</f>
         <v>0</v>
@@ -3973,13 +4218,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="115" t="s">
-        <v>260</v>
-      </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
+        <v>106</v>
+      </c>
+      <c r="B25" s="118" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
       <c r="E25" s="62">
         <f>SUM(D10,E15,E23)</f>
         <v>0</v>
@@ -3987,6 +4232,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B25:D25"/>
@@ -3999,11 +4249,6 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4030,66 +4275,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="111" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="111" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="107" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="107"/>
@@ -4112,12 +4357,12 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="119" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="119"/>
+        <v>103</v>
+      </c>
+      <c r="B9" s="123" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="123"/>
       <c r="D9" s="74" t="s">
         <v>27</v>
       </c>
@@ -4128,32 +4373,33 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C10" s="110"/>
       <c r="D10" s="110"/>
       <c r="E10" s="22">
+        <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="118"/>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="119" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="119"/>
+        <v>103</v>
+      </c>
+      <c r="B12" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="123"/>
       <c r="D12" s="74" t="s">
         <v>27</v>
       </c>
@@ -4164,12 +4410,12 @@
     </row>
     <row r="13" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="B13" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="117"/>
+        <v>158</v>
+      </c>
+      <c r="B13" s="120" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="120"/>
       <c r="D13" s="90"/>
       <c r="E13" s="22">
         <v>0</v>
@@ -4177,12 +4423,12 @@
     </row>
     <row r="14" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="117" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="117"/>
+        <v>159</v>
+      </c>
+      <c r="B14" s="120" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="120"/>
       <c r="D14" s="90"/>
       <c r="E14" s="22">
         <v>0</v>
@@ -4190,12 +4436,12 @@
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="B15" s="117" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="117"/>
+        <v>170</v>
+      </c>
+      <c r="B15" s="120" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="120"/>
       <c r="D15" s="90"/>
       <c r="E15" s="22">
         <v>0</v>
@@ -4203,12 +4449,12 @@
     </row>
     <row r="16" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="117" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="117"/>
+        <v>162</v>
+      </c>
+      <c r="B16" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="120"/>
       <c r="D16" s="90"/>
       <c r="E16" s="22">
         <v>0</v>
@@ -4217,12 +4463,12 @@
     </row>
     <row r="17" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17" s="117" t="s">
-        <v>231</v>
-      </c>
-      <c r="C17" s="117"/>
+        <v>161</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="120"/>
       <c r="D17" s="90"/>
       <c r="E17" s="22">
         <v>0</v>
@@ -4231,12 +4477,12 @@
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="B18" s="117" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="117"/>
+        <v>171</v>
+      </c>
+      <c r="B18" s="120" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="120"/>
       <c r="D18" s="90"/>
       <c r="E18" s="22">
         <v>0</v>
@@ -4245,12 +4491,12 @@
     </row>
     <row r="19" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="B19" s="117" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="117"/>
+        <v>160</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="120"/>
       <c r="D19" s="90"/>
       <c r="E19" s="22">
         <v>0</v>
@@ -4259,12 +4505,12 @@
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>242</v>
-      </c>
-      <c r="C20" s="117"/>
+        <v>172</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="120"/>
       <c r="D20" s="90"/>
       <c r="E20" s="22">
         <v>0</v>
@@ -4273,12 +4519,12 @@
     </row>
     <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="B21" s="120" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="120"/>
+        <v>173</v>
+      </c>
+      <c r="B21" s="122" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" s="122"/>
       <c r="D21" s="90"/>
       <c r="E21" s="22">
         <v>0</v>
@@ -4287,12 +4533,12 @@
     </row>
     <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="120" t="s">
-        <v>244</v>
-      </c>
-      <c r="C22" s="120"/>
+        <v>174</v>
+      </c>
+      <c r="B22" s="122" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="122"/>
       <c r="D22" s="90"/>
       <c r="E22" s="22">
         <v>0</v>
@@ -4301,12 +4547,12 @@
     </row>
     <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="120" t="s">
-        <v>245</v>
-      </c>
-      <c r="C23" s="120"/>
+        <v>175</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="122"/>
       <c r="D23" s="90"/>
       <c r="E23" s="22">
         <v>0</v>
@@ -4315,12 +4561,12 @@
     </row>
     <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="B24" s="120" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="120"/>
+        <v>176</v>
+      </c>
+      <c r="B24" s="122" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="122"/>
       <c r="D24" s="90"/>
       <c r="E24" s="22">
         <v>0</v>
@@ -4330,7 +4576,7 @@
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
       <c r="B25" s="110" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C25" s="110"/>
       <c r="D25" s="110"/>
@@ -4348,12 +4594,12 @@
     </row>
     <row r="27" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="119" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="119"/>
+        <v>103</v>
+      </c>
+      <c r="B27" s="123" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="123"/>
       <c r="D27" s="74" t="s">
         <v>27</v>
       </c>
@@ -4364,12 +4610,12 @@
     </row>
     <row r="28" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="120" t="s">
-        <v>253</v>
-      </c>
-      <c r="C28" s="120"/>
+        <v>177</v>
+      </c>
+      <c r="B28" s="122" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" s="122"/>
       <c r="D28" s="90"/>
       <c r="E28" s="22">
         <v>0</v>
@@ -4377,12 +4623,12 @@
     </row>
     <row r="29" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="B29" s="120" t="s">
-        <v>254</v>
-      </c>
-      <c r="C29" s="120"/>
+        <v>178</v>
+      </c>
+      <c r="B29" s="122" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="122"/>
       <c r="D29" s="90"/>
       <c r="E29" s="22">
         <v>0</v>
@@ -4390,12 +4636,12 @@
     </row>
     <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="B30" s="120" t="s">
-        <v>248</v>
-      </c>
-      <c r="C30" s="120"/>
+        <v>179</v>
+      </c>
+      <c r="B30" s="122" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" s="122"/>
       <c r="D30" s="90"/>
       <c r="E30" s="22">
         <v>0</v>
@@ -4403,12 +4649,12 @@
     </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B31" s="120" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="120"/>
+        <v>180</v>
+      </c>
+      <c r="B31" s="122" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" s="122"/>
       <c r="D31" s="90"/>
       <c r="E31" s="22">
         <v>0</v>
@@ -4417,12 +4663,12 @@
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
       <c r="B32" s="110" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C32" s="110"/>
       <c r="D32" s="110"/>
       <c r="E32" s="62">
-        <f>E10+E25+SUM(E28:E31)</f>
+        <f>SUM(E28:E31)</f>
         <v>0</v>
       </c>
     </row>
@@ -4435,12 +4681,12 @@
     </row>
     <row r="34" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="119" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" s="119"/>
+        <v>103</v>
+      </c>
+      <c r="B34" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="123"/>
       <c r="D34" s="74" t="s">
         <v>27</v>
       </c>
@@ -4452,12 +4698,12 @@
     </row>
     <row r="35" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="B35" s="120" t="s">
-        <v>249</v>
-      </c>
-      <c r="C35" s="120"/>
+        <v>181</v>
+      </c>
+      <c r="B35" s="122" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" s="122"/>
       <c r="D35" s="90"/>
       <c r="E35" s="22">
         <v>0</v>
@@ -4465,12 +4711,12 @@
     </row>
     <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="120" t="s">
-        <v>250</v>
-      </c>
-      <c r="C36" s="120"/>
+        <v>182</v>
+      </c>
+      <c r="B36" s="122" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="122"/>
       <c r="D36" s="90"/>
       <c r="E36" s="22">
         <v>0</v>
@@ -4478,12 +4724,12 @@
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="B37" s="120" t="s">
-        <v>251</v>
-      </c>
-      <c r="C37" s="120"/>
+        <v>183</v>
+      </c>
+      <c r="B37" s="122" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" s="122"/>
       <c r="D37" s="90"/>
       <c r="E37" s="22">
         <v>0</v>
@@ -4492,12 +4738,12 @@
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
       <c r="B38" s="110" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C38" s="110"/>
       <c r="D38" s="110"/>
       <c r="E38" s="62">
-        <f>E10+E25+E32+SUM(E35:E37)</f>
+        <f>SUM(E35:E37)</f>
         <v>0</v>
       </c>
     </row>
@@ -4511,7 +4757,7 @@
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
       <c r="B40" s="110" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C40" s="110"/>
       <c r="D40" s="110"/>
@@ -4529,38 +4775,40 @@
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="B42" s="118" t="s">
-        <v>197</v>
-      </c>
-      <c r="C42" s="118"/>
+        <v>188</v>
+      </c>
+      <c r="B42" s="121" t="s">
+        <v>184</v>
+      </c>
+      <c r="C42" s="121"/>
       <c r="D42" s="26"/>
       <c r="E42" s="22">
+        <f>E46</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="B43" s="118" t="s">
-        <v>198</v>
-      </c>
-      <c r="C43" s="118"/>
+        <v>187</v>
+      </c>
+      <c r="B43" s="121" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="121"/>
       <c r="D43" s="26"/>
       <c r="E43" s="22">
+        <f>E40</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="B44" s="118" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44" s="118"/>
+        <v>186</v>
+      </c>
+      <c r="B44" s="121" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" s="121"/>
       <c r="D44" s="26"/>
       <c r="E44" s="22">
         <v>0</v>
@@ -4569,50 +4817,50 @@
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
       <c r="B45" s="110" t="s">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="C45" s="110"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
       <c r="E45" s="69">
-        <f>E40+E42</f>
+        <f>SUM(E42:E44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
       <c r="B46" s="110" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C46" s="110"/>
       <c r="D46" s="110"/>
       <c r="E46" s="69">
-        <f>'Statement of Financial Position'!D22</f>
+        <f>SUM('Statement of Financial Position'!D18:D19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
       <c r="B47" s="110" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C47" s="110"/>
       <c r="D47" s="110"/>
       <c r="E47" s="69">
-        <f>'Statement of Financial Position'!E22</f>
+        <f>SUM('Statement of Financial Position'!E18:E19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
       <c r="B48" s="110" t="s">
-        <v>123</v>
+        <v>271</v>
       </c>
       <c r="C48" s="110"/>
       <c r="D48" s="110"/>
       <c r="E48" s="69">
-        <f>E47-E46</f>
+        <f>E45-E47</f>
         <v>0</v>
       </c>
     </row>
@@ -4633,7 +4881,7 @@
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
       <c r="B51" s="57" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
@@ -4641,10 +4889,10 @@
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="C52" s="118"/>
+      <c r="B52" s="121" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="121"/>
       <c r="D52" s="90">
         <v>50</v>
       </c>
@@ -4652,10 +4900,10 @@
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="C53" s="118"/>
+      <c r="B53" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="121"/>
       <c r="D53" s="90">
         <v>51</v>
       </c>
@@ -4663,10 +4911,10 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="118" t="s">
-        <v>261</v>
-      </c>
-      <c r="C54" s="118"/>
+      <c r="B54" s="121" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" s="121"/>
       <c r="D54" s="90">
         <v>52</v>
       </c>
@@ -4674,10 +4922,10 @@
     </row>
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
-      <c r="B55" s="118" t="s">
-        <v>262</v>
-      </c>
-      <c r="C55" s="118"/>
+      <c r="B55" s="121" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="121"/>
       <c r="D55" s="90">
         <v>53</v>
       </c>
@@ -4685,10 +4933,10 @@
     </row>
     <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
-      <c r="B56" s="118" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="118"/>
+      <c r="B56" s="121" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="121"/>
       <c r="D56" s="90">
         <v>54</v>
       </c>
@@ -4710,18 +4958,25 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4738,25 +4993,18 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -4782,57 +5030,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="111" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="111" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="107" t="s">
@@ -4855,142 +5103,142 @@
       <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="123" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="123"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
+      <c r="A9" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="122"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
+      <c r="A12" s="125"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="124"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="124"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
+      <c r="A14" s="126"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="124"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
+      <c r="A15" s="126"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
+      <c r="A16" s="126"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
+      <c r="A17" s="126"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="122"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
+      <c r="A18" s="125"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="122"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="122"/>
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
+      <c r="A20" s="125"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="122"/>
-      <c r="B21" s="122"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
+      <c r="A21" s="125"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="125"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122"/>
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
+      <c r="A22" s="125"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="125"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="122"/>
-      <c r="B23" s="122"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="122"/>
+      <c r="A23" s="125"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="122"/>
-      <c r="B24" s="122"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
+      <c r="A24" s="125"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="122"/>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
+      <c r="A25" s="125"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="122"/>
-      <c r="B26" s="122"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
+      <c r="A26" s="125"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="122"/>
-      <c r="B27" s="122"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="122"/>
-      <c r="B28" s="122"/>
-      <c r="C28" s="122"/>
-      <c r="D28" s="122"/>
+      <c r="A28" s="125"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="125"/>
-      <c r="B29" s="125"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
+      <c r="A29" s="124"/>
+      <c r="B29" s="124"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="124"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>27</v>
@@ -5004,6 +5252,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="22">
+        <f>'Statement of Financial Position'!E11</f>
         <v>0</v>
       </c>
       <c r="D31" s="89"/>
@@ -5020,10 +5269,10 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C33" s="22">
         <v>0</v>
@@ -5035,7 +5284,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C34" s="22">
         <v>0</v>
@@ -5047,7 +5296,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C35" s="23">
         <v>0</v>
@@ -5059,7 +5308,7 @@
         <v>2.4</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C36" s="22">
         <v>0</v>
@@ -5071,7 +5320,7 @@
         <v>2.5</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C37" s="22">
         <v>0</v>
@@ -5083,7 +5332,7 @@
         <v>2.6</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C38" s="22">
         <v>0</v>
@@ -5095,7 +5344,7 @@
         <v>2.7</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C39" s="22">
         <v>0</v>
@@ -5107,7 +5356,7 @@
         <v>2.8</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C40" s="22">
         <v>0</v>
@@ -5119,7 +5368,7 @@
         <v>2.9</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C41" s="22">
         <v>0</v>
@@ -5128,10 +5377,10 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C42" s="22">
         <v>0</v>
@@ -5140,10 +5389,10 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C43" s="22">
         <v>0</v>
@@ -5152,10 +5401,10 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C44" s="22">
         <v>0</v>
@@ -5164,10 +5413,10 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C45" s="22">
         <v>0</v>
@@ -5176,10 +5425,10 @@
     </row>
     <row r="46" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C46" s="22">
         <v>0</v>
@@ -5188,10 +5437,10 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C47" s="22">
         <v>0</v>
@@ -5201,7 +5450,7 @@
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33"/>
       <c r="B48" s="45" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C48" s="62">
         <f>SUM(C33:C47)</f>
@@ -5214,9 +5463,10 @@
         <v>3</v>
       </c>
       <c r="B49" s="44" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C49" s="23">
+        <f>'Statement of Financial Position'!E13</f>
         <v>0</v>
       </c>
       <c r="D49" s="24"/>
@@ -5229,6 +5479,7 @@
         <v>36</v>
       </c>
       <c r="C50" s="23">
+        <f>'Statement of Financial Position'!E14</f>
         <v>0</v>
       </c>
       <c r="D50" s="24"/>
@@ -5239,7 +5490,7 @@
         <v>37</v>
       </c>
       <c r="C51" s="62">
-        <f>SUM($C31+$C48+$C49+$C50)</f>
+        <f>SUM(C31,C48:C50)</f>
         <v>0</v>
       </c>
       <c r="D51" s="27"/>
@@ -5252,13 +5503,13 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="74" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D53" s="21" t="s">
         <v>27</v>
@@ -5272,42 +5523,46 @@
         <v>39</v>
       </c>
       <c r="C54" s="23">
+        <f>'Statement of Financial Position'!E18</f>
         <v>0</v>
       </c>
       <c r="D54" s="24"/>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C55" s="23">
+        <f>'Statement of Financial Position'!E19</f>
         <v>0</v>
       </c>
       <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B56" s="44" t="s">
         <v>40</v>
       </c>
       <c r="C56" s="23">
+        <f>'Statement of Financial Position'!E20</f>
         <v>0</v>
       </c>
       <c r="D56" s="89"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="42" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B57" s="44" t="s">
         <v>41</v>
       </c>
       <c r="C57" s="23">
+        <f>'Statement of Financial Position'!E21</f>
         <v>0</v>
       </c>
       <c r="D57" s="24"/>
@@ -5331,13 +5586,13 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="74" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>27</v>
@@ -5345,12 +5600,13 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C61" s="23">
+        <f>'Statement of Financial Position'!E27</f>
         <v>0</v>
       </c>
       <c r="D61" s="24"/>
@@ -5360,9 +5616,10 @@
         <v>10</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C62" s="23">
+        <f>'Statement of Financial Position'!E28</f>
         <v>0</v>
       </c>
       <c r="D62" s="24"/>
@@ -5372,9 +5629,10 @@
         <v>11</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C63" s="23">
+        <f>'Statement of Financial Position'!E29</f>
         <v>0</v>
       </c>
       <c r="D63" s="24"/>
@@ -5387,6 +5645,7 @@
         <v>47</v>
       </c>
       <c r="C64" s="23">
+        <f>'Statement of Financial Position'!E30</f>
         <v>0</v>
       </c>
       <c r="D64" s="24"/>
@@ -5399,6 +5658,7 @@
         <v>48</v>
       </c>
       <c r="C65" s="23">
+        <f>'Statement of Financial Position'!E31</f>
         <v>0</v>
       </c>
       <c r="D65" s="24"/>
@@ -5411,6 +5671,7 @@
         <v>50</v>
       </c>
       <c r="C66" s="23">
+        <f>'Statement of Financial Position'!E32</f>
         <v>0</v>
       </c>
       <c r="D66" s="24"/>
@@ -5418,7 +5679,7 @@
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A67" s="32"/>
       <c r="B67" s="54" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C67" s="71">
         <f>SUM(C61:C66)</f>
@@ -5434,13 +5695,13 @@
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A69" s="74" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D69" s="21" t="s">
         <v>27</v>
@@ -5454,6 +5715,7 @@
         <v>53</v>
       </c>
       <c r="C70" s="88">
+        <f>'Statement of Financial Position'!E36</f>
         <v>0</v>
       </c>
       <c r="D70" s="92"/>
@@ -5466,6 +5728,7 @@
         <v>55</v>
       </c>
       <c r="C71" s="88">
+        <f>'Statement of Financial Position'!E37</f>
         <v>0</v>
       </c>
       <c r="D71" s="92"/>
@@ -5478,6 +5741,7 @@
         <v>57</v>
       </c>
       <c r="C72" s="14">
+        <f>'Statement of Financial Position'!E38</f>
         <v>0</v>
       </c>
       <c r="D72" s="92"/>
@@ -5501,13 +5765,13 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A75" s="74" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D75" s="21" t="s">
         <v>27</v>
@@ -5521,6 +5785,7 @@
         <v>61</v>
       </c>
       <c r="C76" s="14">
+        <f>'Statement of Financial Position'!E42</f>
         <v>0</v>
       </c>
       <c r="D76" s="92"/>
@@ -5533,18 +5798,20 @@
         <v>62</v>
       </c>
       <c r="C77" s="14">
+        <f>'Statement of Financial Position'!E43</f>
         <v>0</v>
       </c>
       <c r="D77" s="92"/>
     </row>
-    <row r="78" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A78" s="98">
         <v>20</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="C78" s="14">
+        <f>'Statement of Financial Position'!E44</f>
         <v>0</v>
       </c>
       <c r="D78" s="92"/>
@@ -5554,9 +5821,10 @@
         <v>21</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C79" s="14">
+        <f>'Statement of Financial Position'!E45</f>
         <v>0</v>
       </c>
       <c r="D79" s="92"/>
@@ -5566,9 +5834,10 @@
         <v>22</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="14">
+        <f>'Statement of Financial Position'!E46</f>
         <v>0</v>
       </c>
       <c r="D80" s="92"/>
@@ -5578,9 +5847,10 @@
         <v>23</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C81" s="14">
+        <f>'Statement of Financial Position'!E47</f>
         <v>0</v>
       </c>
       <c r="D81" s="92"/>
@@ -5590,9 +5860,10 @@
         <v>24</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C82" s="14">
+        <f>'Statement of Financial Position'!E48</f>
         <v>0</v>
       </c>
       <c r="D82" s="92"/>
@@ -5600,7 +5871,7 @@
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A83" s="32"/>
       <c r="B83" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C83" s="63">
         <f>SUM($C76:$C82)</f>
@@ -5610,18 +5881,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5637,6 +5896,18 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5666,61 +5937,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="111" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="111" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="107" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="107"/>
@@ -5740,13 +6011,13 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>27</v>
@@ -5757,9 +6028,10 @@
         <v>25</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C10" s="23">
+        <f>'Statement of Income &amp; Expenses'!E10</f>
         <v>0</v>
       </c>
       <c r="D10" s="89"/>
@@ -5769,9 +6041,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C11" s="23">
+        <f>'Statement of Income &amp; Expenses'!E11</f>
         <v>0</v>
       </c>
       <c r="D11" s="89"/>
@@ -5781,9 +6054,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C12" s="23">
+        <f>'Statement of Income &amp; Expenses'!E12</f>
         <v>0</v>
       </c>
       <c r="D12" s="89"/>
@@ -5793,9 +6067,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C13" s="23">
+        <f>'Statement of Income &amp; Expenses'!E13</f>
         <v>0</v>
       </c>
       <c r="D13" s="89"/>
@@ -5805,9 +6080,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C14" s="23">
+        <f>'Statement of Income &amp; Expenses'!E14</f>
         <v>0</v>
       </c>
       <c r="D14" s="89"/>
@@ -5817,9 +6093,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C15" s="23">
+        <f>'Statement of Income &amp; Expenses'!E15</f>
         <v>0</v>
       </c>
       <c r="D15" s="89"/>
@@ -5829,9 +6106,10 @@
         <v>31</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" s="23">
+        <f>'Statement of Income &amp; Expenses'!E16</f>
         <v>0</v>
       </c>
       <c r="D16" s="89"/>
@@ -5841,9 +6119,10 @@
         <v>32</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" s="23">
+        <f>'Statement of Income &amp; Expenses'!E17</f>
         <v>0</v>
       </c>
       <c r="D17" s="24"/>
@@ -5853,9 +6132,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="23">
+        <f>'Statement of Income &amp; Expenses'!E18</f>
         <v>0</v>
       </c>
       <c r="D18" s="24"/>
@@ -5865,9 +6145,10 @@
         <v>34</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" s="23">
+        <f>'Statement of Income &amp; Expenses'!E19</f>
         <v>0</v>
       </c>
       <c r="D19" s="24"/>
@@ -5875,7 +6156,7 @@
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="54" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C20" s="62">
         <f>SUM(C10:C19)</f>
@@ -5891,13 +6172,13 @@
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C22" s="85" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D22" s="21" t="s">
         <v>27</v>
@@ -5908,9 +6189,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C23" s="23">
+        <f>'Statement of Income &amp; Expenses'!E23</f>
         <v>0</v>
       </c>
       <c r="D23" s="24"/>
@@ -5920,9 +6202,10 @@
         <v>36</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C24" s="23">
+        <f>'Statement of Income &amp; Expenses'!E24</f>
         <v>0</v>
       </c>
       <c r="D24" s="24"/>
@@ -5932,9 +6215,10 @@
         <v>37</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C25" s="23">
+        <f>'Statement of Income &amp; Expenses'!E25</f>
         <v>0</v>
       </c>
       <c r="D25" s="24"/>
@@ -5944,9 +6228,10 @@
         <v>38</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C26" s="23">
+        <f>'Statement of Income &amp; Expenses'!E26</f>
         <v>0</v>
       </c>
       <c r="D26" s="24"/>
@@ -5956,9 +6241,10 @@
         <v>39</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" s="23">
+        <f>'Statement of Income &amp; Expenses'!E27</f>
         <v>0</v>
       </c>
       <c r="D27" s="24"/>
@@ -5968,9 +6254,10 @@
         <v>40</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="23">
+        <f>'Statement of Income &amp; Expenses'!E28</f>
         <v>0</v>
       </c>
       <c r="D28" s="24"/>
@@ -5980,9 +6267,10 @@
         <v>41</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="23">
+        <f>'Statement of Income &amp; Expenses'!E29</f>
         <v>0</v>
       </c>
       <c r="D29" s="24"/>
@@ -5992,9 +6280,10 @@
         <v>42</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" s="23">
+        <f>'Statement of Income &amp; Expenses'!E30</f>
         <v>0</v>
       </c>
       <c r="D30" s="24"/>
@@ -6002,10 +6291,10 @@
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39"/>
       <c r="B31" s="72" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C31" s="73">
-        <f>SUM(C11:C28)</f>
+        <f>SUM(C23:C30)</f>
         <v>0</v>
       </c>
       <c r="D31" s="39"/>
@@ -6018,13 +6307,13 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="C33" s="99" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>27</v>
@@ -6035,9 +6324,10 @@
         <v>43</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C34" s="23">
+        <f>'Statement of Income &amp; Expenses'!E34</f>
         <v>0</v>
       </c>
       <c r="D34" s="24"/>
@@ -6047,9 +6337,10 @@
         <v>44</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C35" s="23">
+        <f>'Statement of Income &amp; Expenses'!E35</f>
         <v>0</v>
       </c>
       <c r="D35" s="24"/>
@@ -6059,9 +6350,10 @@
         <v>45</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C36" s="23">
+        <f>'Statement of Income &amp; Expenses'!E36</f>
         <v>0</v>
       </c>
       <c r="D36" s="24"/>
@@ -6071,9 +6363,10 @@
         <v>46</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C37" s="23">
+        <f>'Statement of Income &amp; Expenses'!E37</f>
         <v>0</v>
       </c>
       <c r="D37" s="24"/>
@@ -6083,9 +6376,10 @@
         <v>47</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C38" s="23">
+        <f>'Statement of Income &amp; Expenses'!E38</f>
         <v>0</v>
       </c>
       <c r="D38" s="24"/>
@@ -6095,9 +6389,10 @@
         <v>48</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C39" s="23">
+        <f>'Statement of Income &amp; Expenses'!E39</f>
         <v>0</v>
       </c>
       <c r="D39" s="24"/>
@@ -6105,10 +6400,10 @@
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="30"/>
       <c r="B40" s="35" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C40" s="63">
-        <f>SUM(C34:C39)</f>
+        <f>SUM(C20,C31,C34:C39)</f>
         <v>0</v>
       </c>
       <c r="D40" s="100"/>
@@ -6149,217 +6444,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="130" t="str">
+      <c r="B2" s="133" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="130" t="str">
+      <c r="B3" s="133" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="131">
+      <c r="B4" s="134">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="131">
+      <c r="B5" s="134">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="131"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="132" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
+      <c r="A6" s="130" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="130"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="132"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
+      <c r="A7" s="130"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="132"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
+      <c r="A8" s="130"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>125</v>
+        <v>273</v>
       </c>
       <c r="C9" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
-      <c r="B10" s="30"/>
+      <c r="B10" s="30" t="s">
+        <v>184</v>
+      </c>
       <c r="C10" s="81">
-        <v>0</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
+        <f>'Cash Flows Statement - indirect'!E46</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
-      <c r="B11" s="30"/>
+      <c r="B11" s="30" t="s">
+        <v>274</v>
+      </c>
       <c r="C11" s="81">
-        <v>0</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
+        <f>'Cash Flows Statement - indirect'!E40</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
-      <c r="B12" s="30"/>
+      <c r="B12" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="C12" s="81">
-        <v>0</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
+        <f>'Cash Flows Statement - indirect'!E44</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
         <v>49</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C13" s="63">
         <f>SUM(C10:C12)</f>
@@ -6391,25 +6695,25 @@
     </row>
     <row r="15" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C15" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="128"/>
-      <c r="L15" s="128"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6417,15 +6721,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="127"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6433,15 +6737,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="131"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6449,22 +6753,22 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-    </row>
-    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="131"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
         <v>50</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>163</v>
+        <v>276</v>
       </c>
       <c r="C19" s="82">
         <f>SUM(C16:C18)</f>
@@ -6496,25 +6800,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C21" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6522,15 +6826,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6538,15 +6842,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="127"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6554,22 +6858,22 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="127"/>
-    </row>
-    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
         <v>51</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>164</v>
+        <v>277</v>
       </c>
       <c r="C25" s="82">
         <f>SUM(C22:C24)</f>
@@ -6601,25 +6905,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B27" s="80" t="s">
-        <v>127</v>
+        <v>278</v>
       </c>
       <c r="C27" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="128"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="128"/>
-      <c r="K27" s="128"/>
-      <c r="L27" s="128"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6627,15 +6931,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="127"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6643,15 +6947,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6659,22 +6963,22 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
-    </row>
-    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
         <v>52</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C31" s="82">
         <f>SUM(C28:C30)</f>
@@ -6706,25 +7010,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B33" s="80" t="s">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="C33" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -6732,15 +7036,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="127"/>
-      <c r="L34" s="127"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="131"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -6748,15 +7052,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+      <c r="J35" s="131"/>
+      <c r="K35" s="131"/>
+      <c r="L35" s="131"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -6764,22 +7068,22 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
-      <c r="K36" s="127"/>
-      <c r="L36" s="127"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="131"/>
+      <c r="K36" s="131"/>
+      <c r="L36" s="131"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
         <v>53</v>
       </c>
       <c r="B37" s="54" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C37" s="82">
         <f>SUM(C34:C36)</f>
@@ -6811,25 +7115,25 @@
     </row>
     <row r="39" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C39" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="128"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="128"/>
-      <c r="J39" s="128"/>
-      <c r="K39" s="128"/>
-      <c r="L39" s="128"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="132"/>
+      <c r="I39" s="132"/>
+      <c r="J39" s="132"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="132"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -6837,15 +7141,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="127"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="127"/>
+      <c r="D40" s="131"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
+      <c r="J40" s="131"/>
+      <c r="K40" s="131"/>
+      <c r="L40" s="131"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -6853,15 +7157,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="127"/>
-      <c r="L41" s="127"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="131"/>
+      <c r="I41" s="131"/>
+      <c r="J41" s="131"/>
+      <c r="K41" s="131"/>
+      <c r="L41" s="131"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -6869,54 +7173,39 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="127"/>
-      <c r="E42" s="127"/>
-      <c r="F42" s="127"/>
-      <c r="G42" s="127"/>
-      <c r="H42" s="127"/>
-      <c r="I42" s="127"/>
-      <c r="J42" s="127"/>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="131"/>
+      <c r="I42" s="131"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="131"/>
+      <c r="L42" s="131"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
         <v>54</v>
       </c>
       <c r="B43" s="54" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C43" s="82">
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="129"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-      <c r="L43" s="129"/>
+      <c r="D43" s="135"/>
+      <c r="E43" s="135"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="135"/>
+      <c r="H43" s="135"/>
+      <c r="I43" s="135"/>
+      <c r="J43" s="135"/>
+      <c r="K43" s="135"/>
+      <c r="L43" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D15:L15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="D33:L33"/>
@@ -6933,6 +7222,21 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
@@ -6940,4 +7244,370 @@
     <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2F75B5"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="74" customWidth="1"/>
+    <col min="3" max="3" width="82" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="105" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+    </row>
+    <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="138" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+    </row>
+    <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="136" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+    </row>
+    <row r="5" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="111" t="str">
+        <f>'General information'!B2</f>
+        <v>No-ProfitName LegalForm</v>
+      </c>
+      <c r="C5" s="137"/>
+      <c r="D5" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="101">
+        <f>'General information'!B8</f>
+        <v>45292</v>
+      </c>
+      <c r="C6" s="101">
+        <f>'General information'!B9</f>
+        <v>45657</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="102" t="str">
+        <f>'General information'!B21</f>
+        <v>EUR</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="136" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+    </row>
+    <row r="10" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="123" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+    </row>
+    <row r="11" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="123" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+    </row>
+    <row r="19" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="123" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="123"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
+    </row>
+    <row r="26" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="12" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C31" s="24"/>
+      <c r="D31" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="123" t="s">
+        <v>346</v>
+      </c>
+      <c r="B33" s="123"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="123"/>
+    </row>
+    <row r="34" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="136" t="s">
+        <v>347</v>
+      </c>
+      <c r="B34" s="137"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+    </row>
+    <row r="35" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="136" t="s">
+        <v>348</v>
+      </c>
+      <c r="B35" s="137"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;CINPAS - Explanatory notes&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/noprofit/en/11255/inpas-template.xlsx
+++ b/noprofit/en/11255/inpas-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C27F2B-9ECA-48EA-98F6-1411ACF05CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9637BA-DD0C-4269-8125-577304F3EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -634,15 +634,6 @@
     <t>[+] Grants and donations restricted Project 1</t>
   </si>
   <si>
-    <t>Restricted Funds Project 1</t>
-  </si>
-  <si>
-    <t>Restricted Funds Project 2</t>
-  </si>
-  <si>
-    <t>Restricted Funds Project 3</t>
-  </si>
-  <si>
     <t>Grants restricted Project 2</t>
   </si>
   <si>
@@ -721,15 +712,6 @@
     <t>[+/-] Investment property</t>
   </si>
   <si>
-    <t>[+/-] Restricted Funds Project 1</t>
-  </si>
-  <si>
-    <t>[+/-] Restricted Funds Project 2</t>
-  </si>
-  <si>
-    <t>[+/-] Restricted Funds Project 3</t>
-  </si>
-  <si>
     <t>[+/-] Funds without restrictions</t>
   </si>
   <si>
@@ -1100,6 +1082,24 @@
   </si>
   <si>
     <t>Source: INPAS 2025, The Standard (https://www.inprf.org). Paragraph references are shown on the right. This worksheet is a preparation aid; it is not, by itself, a statement of full INPAS compliance.</t>
+  </si>
+  <si>
+    <t>Restricted Fund A</t>
+  </si>
+  <si>
+    <t>Restricted Fund B</t>
+  </si>
+  <si>
+    <t>Restricted Fund C</t>
+  </si>
+  <si>
+    <t>[+/-] Restricted Fund A</t>
+  </si>
+  <si>
+    <t>[+/-] Restricted Fund B</t>
+  </si>
+  <si>
+    <t>[+/-] Restricted Fund C</t>
   </si>
 </sst>
 </file>
@@ -1586,6 +1586,27 @@
     <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1594,27 +1615,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2078,324 +2078,324 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="104">
+      <c r="B8" s="111">
         <v>45292</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="104">
+      <c r="B9" s="111">
         <v>45657</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="104" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
+      <c r="B10" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="96"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="96"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="104" t="s">
-        <v>247</v>
-      </c>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
+      <c r="B22" s="111" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
-      <c r="B23" s="104" t="s">
-        <v>246</v>
-      </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
+      <c r="B23" s="111" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
-      <c r="B24" s="104" t="s">
-        <v>238</v>
-      </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
+      <c r="B24" s="111" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
-      <c r="B25" s="104" t="s">
-        <v>248</v>
-      </c>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
+      <c r="B25" s="111" t="s">
+        <v>242</v>
+      </c>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
-      <c r="B26" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
+      <c r="B26" s="111" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
-      <c r="B27" s="104" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
+      <c r="B27" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
-      <c r="B28" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
+      <c r="B28" s="111" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2449,84 +2449,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -2549,12 +2549,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -2649,12 +2649,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
@@ -2782,19 +2782,19 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>193</v>
+        <v>343</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>343</v>
       </c>
       <c r="C27" s="90">
         <v>9</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>194</v>
+        <v>344</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>344</v>
       </c>
       <c r="C28" s="90">
         <v>10</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>195</v>
+        <v>345</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>345</v>
       </c>
       <c r="C29" s="90">
         <v>11</v>
@@ -2915,12 +2915,12 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
@@ -2997,12 +2997,12 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="110" t="s">
+      <c r="B41" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="110"/>
-      <c r="D41" s="110"/>
-      <c r="E41" s="110"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="107"/>
+      <c r="E41" s="107"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C44" s="90">
         <v>20</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="110" t="s">
+      <c r="B49" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="107"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="110" t="s">
+      <c r="B50" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="107"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -3171,11 +3171,11 @@
       <c r="A53" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="109" t="str">
+      <c r="B53" s="106" t="str">
         <f>IF(ABS(D53)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="109"/>
+      <c r="C53" s="106"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -3185,12 +3185,12 @@
       <c r="A54" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="108" t="str">
+      <c r="B54" s="105" t="str">
         <f>IF(ABS(E54)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="108"/>
-      <c r="D54" s="108"/>
+      <c r="C54" s="105"/>
+      <c r="D54" s="105"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -3331,27 +3331,27 @@
       <c r="E5" s="116"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="12" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C12" s="91">
         <v>27</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="13" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C13" s="91">
         <v>28</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="14" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C14" s="91">
         <v>29</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="15" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C15" s="91">
         <v>30</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="23" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C23" s="91">
         <v>35</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="24" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C24" s="91">
         <v>36</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="25" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C25" s="91">
         <v>37</v>
@@ -3636,10 +3636,10 @@
     </row>
     <row r="26" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C26" s="91">
         <v>38</v>
@@ -3765,7 +3765,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C34" s="91">
         <v>43</v>
@@ -3782,7 +3782,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C35" s="91">
         <v>44</v>
@@ -3799,7 +3799,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C36" s="91">
         <v>45</v>
@@ -3816,7 +3816,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C37" s="91">
         <v>46</v>
@@ -3833,7 +3833,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C38" s="91">
         <v>47</v>
@@ -3850,7 +3850,7 @@
         <v>101</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C39" s="91">
         <v>48</v>
@@ -3865,7 +3865,7 @@
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40" s="86" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C40" s="86"/>
       <c r="D40" s="87">
@@ -3880,7 +3880,7 @@
     <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="64" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C41" s="64"/>
       <c r="D41" s="66">
@@ -3931,13 +3931,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3946,72 +3946,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="107" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -4035,7 +4035,7 @@
         <v>102</v>
       </c>
       <c r="B10" s="117" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C10" s="117"/>
       <c r="D10" s="14">
@@ -4056,7 +4056,7 @@
         <v>103</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C12" s="75"/>
       <c r="D12" s="74">
@@ -4087,7 +4087,7 @@
         <v>105</v>
       </c>
       <c r="B14" s="119" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C14" s="119"/>
       <c r="D14" s="119"/>
@@ -4098,7 +4098,7 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
       <c r="B15" s="118" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C15" s="118"/>
       <c r="D15" s="118"/>
@@ -4119,7 +4119,7 @@
         <v>103</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="76">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B18" s="120" t="s">
-        <v>222</v>
+        <v>346</v>
       </c>
       <c r="C18" s="120"/>
       <c r="D18" s="120"/>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B19" s="120" t="s">
-        <v>223</v>
+        <v>347</v>
       </c>
       <c r="C19" s="120"/>
       <c r="D19" s="120"/>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B20" s="120" t="s">
-        <v>224</v>
+        <v>348</v>
       </c>
       <c r="C20" s="120"/>
       <c r="D20" s="120"/>
@@ -4175,7 +4175,7 @@
         <v>156</v>
       </c>
       <c r="B21" s="120" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C21" s="120"/>
       <c r="D21" s="120"/>
@@ -4188,7 +4188,7 @@
         <v>157</v>
       </c>
       <c r="B22" s="119" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C22" s="119"/>
       <c r="D22" s="119"/>
@@ -4199,7 +4199,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="118" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C23" s="118"/>
       <c r="D23" s="118"/>
@@ -4221,7 +4221,7 @@
         <v>106</v>
       </c>
       <c r="B25" s="118" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C25" s="118"/>
       <c r="D25" s="118"/>
@@ -4275,85 +4275,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>245</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -4375,11 +4375,11 @@
       <c r="A10" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
       <c r="E10" s="22">
         <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>158</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C13" s="120"/>
       <c r="D13" s="90"/>
@@ -4426,7 +4426,7 @@
         <v>159</v>
       </c>
       <c r="B14" s="120" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C14" s="120"/>
       <c r="D14" s="90"/>
@@ -4439,7 +4439,7 @@
         <v>170</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C15" s="120"/>
       <c r="D15" s="90"/>
@@ -4452,7 +4452,7 @@
         <v>162</v>
       </c>
       <c r="B16" s="120" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C16" s="120"/>
       <c r="D16" s="90"/>
@@ -4466,7 +4466,7 @@
         <v>161</v>
       </c>
       <c r="B17" s="120" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C17" s="120"/>
       <c r="D17" s="90"/>
@@ -4480,7 +4480,7 @@
         <v>171</v>
       </c>
       <c r="B18" s="120" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C18" s="120"/>
       <c r="D18" s="90"/>
@@ -4494,7 +4494,7 @@
         <v>160</v>
       </c>
       <c r="B19" s="120" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C19" s="120"/>
       <c r="D19" s="90"/>
@@ -4508,7 +4508,7 @@
         <v>172</v>
       </c>
       <c r="B20" s="120" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C20" s="120"/>
       <c r="D20" s="90"/>
@@ -4522,7 +4522,7 @@
         <v>173</v>
       </c>
       <c r="B21" s="122" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C21" s="122"/>
       <c r="D21" s="90"/>
@@ -4536,7 +4536,7 @@
         <v>174</v>
       </c>
       <c r="B22" s="122" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C22" s="122"/>
       <c r="D22" s="90"/>
@@ -4550,7 +4550,7 @@
         <v>175</v>
       </c>
       <c r="B23" s="122" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C23" s="122"/>
       <c r="D23" s="90"/>
@@ -4564,7 +4564,7 @@
         <v>176</v>
       </c>
       <c r="B24" s="122" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C24" s="122"/>
       <c r="D24" s="90"/>
@@ -4575,11 +4575,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4613,7 +4613,7 @@
         <v>177</v>
       </c>
       <c r="B28" s="122" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C28" s="122"/>
       <c r="D28" s="90"/>
@@ -4626,7 +4626,7 @@
         <v>178</v>
       </c>
       <c r="B29" s="122" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C29" s="122"/>
       <c r="D29" s="90"/>
@@ -4639,7 +4639,7 @@
         <v>179</v>
       </c>
       <c r="B30" s="122" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C30" s="122"/>
       <c r="D30" s="90"/>
@@ -4652,7 +4652,7 @@
         <v>180</v>
       </c>
       <c r="B31" s="122" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C31" s="122"/>
       <c r="D31" s="90"/>
@@ -4662,11 +4662,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
       <c r="E32" s="62">
         <f>SUM(E28:E31)</f>
         <v>0</v>
@@ -4701,7 +4701,7 @@
         <v>181</v>
       </c>
       <c r="B35" s="122" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C35" s="122"/>
       <c r="D35" s="90"/>
@@ -4714,7 +4714,7 @@
         <v>182</v>
       </c>
       <c r="B36" s="122" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C36" s="122"/>
       <c r="D36" s="90"/>
@@ -4727,7 +4727,7 @@
         <v>183</v>
       </c>
       <c r="B37" s="122" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C37" s="122"/>
       <c r="D37" s="90"/>
@@ -4737,11 +4737,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="110" t="s">
+      <c r="B38" s="107" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
       <c r="E38" s="62">
         <f>SUM(E35:E37)</f>
         <v>0</v>
@@ -4756,11 +4756,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="110" t="s">
+      <c r="B40" s="107" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="110"/>
-      <c r="D40" s="110"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="107"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4792,7 +4792,7 @@
         <v>187</v>
       </c>
       <c r="B43" s="121" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C43" s="121"/>
       <c r="D43" s="26"/>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="110" t="s">
-        <v>270</v>
-      </c>
-      <c r="C45" s="110"/>
+      <c r="B45" s="107" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" s="107"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4830,11 +4830,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="110" t="s">
+      <c r="B46" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="110"/>
-      <c r="D46" s="110"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
       <c r="E46" s="69">
         <f>SUM('Statement of Financial Position'!D18:D19)</f>
         <v>0</v>
@@ -4842,11 +4842,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="110"/>
-      <c r="D47" s="110"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="107"/>
       <c r="E47" s="69">
         <f>SUM('Statement of Financial Position'!E18:E19)</f>
         <v>0</v>
@@ -4854,11 +4854,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="110" t="s">
-        <v>271</v>
-      </c>
-      <c r="C48" s="110"/>
-      <c r="D48" s="110"/>
+      <c r="B48" s="107" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="107"/>
+      <c r="D48" s="107"/>
       <c r="E48" s="69">
         <f>E45-E47</f>
         <v>0</v>
@@ -4912,7 +4912,7 @@
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
       <c r="B54" s="121" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C54" s="121"/>
       <c r="D54" s="90">
@@ -4923,7 +4923,7 @@
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
       <c r="B55" s="121" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C55" s="121"/>
       <c r="D55" s="90">
@@ -5042,65 +5042,65 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
+      <c r="A6" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="128" t="s">
@@ -5603,7 +5603,7 @@
         <v>167</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>193</v>
+        <v>343</v>
       </c>
       <c r="C61" s="23">
         <f>'Statement of Financial Position'!E27</f>
@@ -5616,7 +5616,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>194</v>
+        <v>344</v>
       </c>
       <c r="C62" s="23">
         <f>'Statement of Financial Position'!E28</f>
@@ -5629,7 +5629,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="C63" s="23">
         <f>'Statement of Financial Position'!E29</f>
@@ -5808,7 +5808,7 @@
         <v>20</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C78" s="14">
         <f>'Statement of Financial Position'!E44</f>
@@ -5949,65 +5949,65 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6054,7 +6054,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C12" s="23">
         <f>'Statement of Income &amp; Expenses'!E12</f>
@@ -6067,7 +6067,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C13" s="23">
         <f>'Statement of Income &amp; Expenses'!E13</f>
@@ -6080,7 +6080,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C14" s="23">
         <f>'Statement of Income &amp; Expenses'!E14</f>
@@ -6093,7 +6093,7 @@
         <v>30</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C15" s="23">
         <f>'Statement of Income &amp; Expenses'!E15</f>
@@ -6189,7 +6189,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C23" s="23">
         <f>'Statement of Income &amp; Expenses'!E23</f>
@@ -6202,7 +6202,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C24" s="23">
         <f>'Statement of Income &amp; Expenses'!E24</f>
@@ -6215,7 +6215,7 @@
         <v>37</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C25" s="23">
         <f>'Statement of Income &amp; Expenses'!E25</f>
@@ -6228,7 +6228,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C26" s="23">
         <f>'Statement of Income &amp; Expenses'!E26</f>
@@ -6310,7 +6310,7 @@
         <v>121</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C33" s="99" t="s">
         <v>123</v>
@@ -6324,7 +6324,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C34" s="23">
         <f>'Statement of Income &amp; Expenses'!E34</f>
@@ -6337,7 +6337,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C35" s="23">
         <f>'Statement of Income &amp; Expenses'!E35</f>
@@ -6350,7 +6350,7 @@
         <v>45</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C36" s="23">
         <f>'Statement of Income &amp; Expenses'!E36</f>
@@ -6363,7 +6363,7 @@
         <v>46</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C37" s="23">
         <f>'Statement of Income &amp; Expenses'!E37</f>
@@ -6376,7 +6376,7 @@
         <v>47</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C38" s="23">
         <f>'Statement of Income &amp; Expenses'!E38</f>
@@ -6389,7 +6389,7 @@
         <v>48</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C39" s="23">
         <f>'Statement of Income &amp; Expenses'!E39</f>
@@ -6400,7 +6400,7 @@
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="30"/>
       <c r="B40" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C40" s="63">
         <f>SUM(C20,C31,C34:C39)</f>
@@ -6537,7 +6537,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="130" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B6" s="130"/>
       <c r="C6" s="130"/>
@@ -6584,7 +6584,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C9" s="83" t="s">
         <v>123</v>
@@ -6623,7 +6623,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
       <c r="B11" s="30" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C11" s="81">
         <f>'Cash Flows Statement - indirect'!E40</f>
@@ -6663,7 +6663,7 @@
         <v>49</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C13" s="63">
         <f>SUM(C10:C12)</f>
@@ -6768,7 +6768,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C19" s="82">
         <f>SUM(C16:C18)</f>
@@ -6873,7 +6873,7 @@
         <v>51</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C25" s="82">
         <f>SUM(C22:C24)</f>
@@ -6908,7 +6908,7 @@
         <v>121</v>
       </c>
       <c r="B27" s="80" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C27" s="83" t="s">
         <v>123</v>
@@ -6978,7 +6978,7 @@
         <v>52</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C31" s="82">
         <f>SUM(C28:C30)</f>
@@ -7013,7 +7013,7 @@
         <v>121</v>
       </c>
       <c r="B33" s="80" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C33" s="83" t="s">
         <v>123</v>
@@ -7083,7 +7083,7 @@
         <v>53</v>
       </c>
       <c r="B37" s="54" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C37" s="82">
         <f>SUM(C34:C36)</f>
@@ -7262,16 +7262,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
-        <v>282</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
+      <c r="A1" s="112" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="138" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B2" s="138"/>
       <c r="C2" s="138"/>
@@ -7279,7 +7279,7 @@
     </row>
     <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="136" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="137"/>
@@ -7287,20 +7287,20 @@
     </row>
     <row r="5" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="B5" s="111" t="str">
+        <v>279</v>
+      </c>
+      <c r="B5" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
       <c r="C5" s="137"/>
       <c r="D5" s="12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B6" s="101">
         <f>'General information'!B8</f>
@@ -7311,25 +7311,25 @@
         <v>45657</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B7" s="102" t="str">
         <f>'General information'!B21</f>
         <v>EUR</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="136" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B8" s="137"/>
       <c r="C8" s="137"/>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="10" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="123" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B10" s="123"/>
       <c r="C10" s="123"/>
@@ -7345,81 +7345,81 @@
     </row>
     <row r="11" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C12" s="24"/>
       <c r="D12" s="12" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C13" s="24"/>
       <c r="D13" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C14" s="24"/>
       <c r="D14" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C15" s="24"/>
       <c r="D15" s="12" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="12" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="123" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B18" s="123"/>
       <c r="C18" s="123"/>
@@ -7427,67 +7427,67 @@
     </row>
     <row r="19" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="12" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C20" s="24"/>
       <c r="D20" s="12" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C21" s="24"/>
       <c r="D21" s="12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="123" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B25" s="123"/>
       <c r="C25" s="123"/>
@@ -7495,79 +7495,79 @@
     </row>
     <row r="26" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="12" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="38" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="12" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="12" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="12" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="38" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="12" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="38" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C31" s="24"/>
       <c r="D31" s="12" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="123" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B33" s="123"/>
       <c r="C33" s="123"/>
@@ -7575,7 +7575,7 @@
     </row>
     <row r="34" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="136" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B34" s="137"/>
       <c r="C34" s="137"/>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="35" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="136" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>

--- a/noprofit/en/11255/inpas-template.xlsx
+++ b/noprofit/en/11255/inpas-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9637BA-DD0C-4269-8125-577304F3EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE7DD58-AD2F-4706-809F-E50895CADAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="352">
   <si>
     <t>Company name and legal form</t>
   </si>
@@ -1100,6 +1100,15 @@
   </si>
   <si>
     <t>[+/-] Restricted Fund C</t>
+  </si>
+  <si>
+    <t>Disclose fundraising costs by category, including direct, shared and support costs where applicable. Explain the methods used to allocate and apportion these costs, and disclose the information required for activities serving more than one purpose.</t>
+  </si>
+  <si>
+    <t>Fundraising costs</t>
+  </si>
+  <si>
+    <t>D3</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1306,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1586,6 +1595,24 @@
     <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1598,24 +1625,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1640,47 +1649,47 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1688,6 +1697,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2078,327 +2090,333 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="105" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="113" t="s">
+      <c r="B4" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="113" t="s">
+      <c r="B5" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="113"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="113"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="111">
+      <c r="B8" s="104">
         <v>45292</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="111">
+      <c r="B9" s="104">
         <v>45657</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="111"/>
-      <c r="G9" s="111"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="104" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="96"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="96"/>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="111" t="s">
+      <c r="B17" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
-      <c r="G17" s="111"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
-      <c r="B18" s="111" t="s">
+      <c r="B18" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="111"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
-      <c r="B19" s="111" t="s">
+      <c r="B19" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
-      <c r="B20" s="111" t="s">
+      <c r="B20" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="111" t="s">
+      <c r="B22" s="104" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
-      <c r="B23" s="111" t="s">
+      <c r="B23" s="104" t="s">
         <v>240</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
-      <c r="B24" s="111" t="s">
+      <c r="B24" s="104" t="s">
         <v>232</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
-      <c r="B25" s="111" t="s">
+      <c r="B25" s="104" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
-      <c r="B26" s="111" t="s">
+      <c r="B26" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="104" t="s">
         <v>238</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
-      <c r="B28" s="111" t="s">
+      <c r="B28" s="104" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="111"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2415,12 +2433,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2449,84 +2461,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="107" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>241</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -2549,12 +2561,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -2649,12 +2661,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
@@ -2782,12 +2794,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
@@ -2915,12 +2927,12 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
@@ -2997,12 +3009,12 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="107" t="s">
+      <c r="B41" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
+      <c r="C41" s="113"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="113"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
@@ -3125,10 +3137,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="107"/>
+      <c r="C49" s="113"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -3140,10 +3152,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="107" t="s">
+      <c r="B50" s="113" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="107"/>
+      <c r="C50" s="113"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -3171,11 +3183,11 @@
       <c r="A53" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="106" t="str">
+      <c r="B53" s="112" t="str">
         <f>IF(ABS(D53)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="106"/>
+      <c r="C53" s="112"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -3185,12 +3197,12 @@
       <c r="A54" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="105" t="str">
+      <c r="B54" s="111" t="str">
         <f>IF(ABS(E54)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -3204,11 +3216,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B53:C53"/>
@@ -3219,6 +3226,11 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B53">
@@ -3331,27 +3343,27 @@
       <c r="E5" s="116"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3931,13 +3943,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3946,72 +3958,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="107" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -4232,11 +4244,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B25:D25"/>
@@ -4249,6 +4256,11 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4275,94 +4287,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="107" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="123" t="s">
+      <c r="B9" s="122" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="123"/>
+      <c r="C9" s="122"/>
       <c r="D9" s="74" t="s">
         <v>27</v>
       </c>
@@ -4375,11 +4387,11 @@
       <c r="A10" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="113" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
       <c r="E10" s="22">
         <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
@@ -4396,10 +4408,10 @@
       <c r="A12" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="123"/>
+      <c r="C12" s="122"/>
       <c r="D12" s="74" t="s">
         <v>27</v>
       </c>
@@ -4521,10 +4533,10 @@
       <c r="A21" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="123" t="s">
         <v>223</v>
       </c>
-      <c r="C21" s="122"/>
+      <c r="C21" s="123"/>
       <c r="D21" s="90"/>
       <c r="E21" s="22">
         <v>0</v>
@@ -4535,10 +4547,10 @@
       <c r="A22" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="123" t="s">
         <v>224</v>
       </c>
-      <c r="C22" s="122"/>
+      <c r="C22" s="123"/>
       <c r="D22" s="90"/>
       <c r="E22" s="22">
         <v>0</v>
@@ -4549,10 +4561,10 @@
       <c r="A23" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="B23" s="122" t="s">
+      <c r="B23" s="123" t="s">
         <v>225</v>
       </c>
-      <c r="C23" s="122"/>
+      <c r="C23" s="123"/>
       <c r="D23" s="90"/>
       <c r="E23" s="22">
         <v>0</v>
@@ -4563,10 +4575,10 @@
       <c r="A24" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="123" t="s">
         <v>226</v>
       </c>
-      <c r="C24" s="122"/>
+      <c r="C24" s="123"/>
       <c r="D24" s="90"/>
       <c r="E24" s="22">
         <v>0</v>
@@ -4575,11 +4587,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4596,10 +4608,10 @@
       <c r="A27" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="123" t="s">
+      <c r="B27" s="122" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="123"/>
+      <c r="C27" s="122"/>
       <c r="D27" s="74" t="s">
         <v>27</v>
       </c>
@@ -4612,10 +4624,10 @@
       <c r="A28" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="122"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="90"/>
       <c r="E28" s="22">
         <v>0</v>
@@ -4625,10 +4637,10 @@
       <c r="A29" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="122" t="s">
+      <c r="B29" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="122"/>
+      <c r="C29" s="123"/>
       <c r="D29" s="90"/>
       <c r="E29" s="22">
         <v>0</v>
@@ -4638,10 +4650,10 @@
       <c r="A30" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="B30" s="122" t="s">
+      <c r="B30" s="123" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="122"/>
+      <c r="C30" s="123"/>
       <c r="D30" s="90"/>
       <c r="E30" s="22">
         <v>0</v>
@@ -4651,10 +4663,10 @@
       <c r="A31" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="122" t="s">
+      <c r="B31" s="123" t="s">
         <v>262</v>
       </c>
-      <c r="C31" s="122"/>
+      <c r="C31" s="123"/>
       <c r="D31" s="90"/>
       <c r="E31" s="22">
         <v>0</v>
@@ -4662,11 +4674,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="113"/>
       <c r="E32" s="62">
         <f>SUM(E28:E31)</f>
         <v>0</v>
@@ -4683,10 +4695,10 @@
       <c r="A34" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="123" t="s">
+      <c r="B34" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="123"/>
+      <c r="C34" s="122"/>
       <c r="D34" s="74" t="s">
         <v>27</v>
       </c>
@@ -4700,10 +4712,10 @@
       <c r="A35" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="B35" s="122" t="s">
+      <c r="B35" s="123" t="s">
         <v>227</v>
       </c>
-      <c r="C35" s="122"/>
+      <c r="C35" s="123"/>
       <c r="D35" s="90"/>
       <c r="E35" s="22">
         <v>0</v>
@@ -4713,10 +4725,10 @@
       <c r="A36" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="B36" s="122" t="s">
+      <c r="B36" s="123" t="s">
         <v>228</v>
       </c>
-      <c r="C36" s="122"/>
+      <c r="C36" s="123"/>
       <c r="D36" s="90"/>
       <c r="E36" s="22">
         <v>0</v>
@@ -4726,10 +4738,10 @@
       <c r="A37" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="B37" s="122" t="s">
+      <c r="B37" s="123" t="s">
         <v>229</v>
       </c>
-      <c r="C37" s="122"/>
+      <c r="C37" s="123"/>
       <c r="D37" s="90"/>
       <c r="E37" s="22">
         <v>0</v>
@@ -4737,11 +4749,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="113" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
+      <c r="C38" s="113"/>
+      <c r="D38" s="113"/>
       <c r="E38" s="62">
         <f>SUM(E35:E37)</f>
         <v>0</v>
@@ -4756,11 +4768,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="107" t="s">
+      <c r="B40" s="113" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
+      <c r="C40" s="113"/>
+      <c r="D40" s="113"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4816,10 +4828,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="113" t="s">
         <v>264</v>
       </c>
-      <c r="C45" s="107"/>
+      <c r="C45" s="113"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4830,11 +4842,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="113" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
+      <c r="C46" s="113"/>
+      <c r="D46" s="113"/>
       <c r="E46" s="69">
         <f>SUM('Statement of Financial Position'!D18:D19)</f>
         <v>0</v>
@@ -4842,11 +4854,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="107" t="s">
+      <c r="B47" s="113" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
+      <c r="C47" s="113"/>
+      <c r="D47" s="113"/>
       <c r="E47" s="69">
         <f>SUM('Statement of Financial Position'!E18:E19)</f>
         <v>0</v>
@@ -4854,11 +4866,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="107" t="s">
+      <c r="B48" s="113" t="s">
         <v>265</v>
       </c>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
+      <c r="C48" s="113"/>
+      <c r="D48" s="113"/>
       <c r="E48" s="69">
         <f>E45-E47</f>
         <v>0</v>
@@ -4958,25 +4970,18 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4993,18 +4998,25 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -5030,85 +5042,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="107" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="128" t="s">
+      <c r="A9" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="125"/>
@@ -5129,34 +5141,34 @@
       <c r="D12" s="125"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="126"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
+      <c r="A13" s="127"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="126"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
+      <c r="A14" s="127"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="126"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
+      <c r="A15" s="127"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="126"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
+      <c r="A16" s="127"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="126"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
+      <c r="A17" s="127"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="125"/>
@@ -5225,10 +5237,10 @@
       <c r="D28" s="125"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="124"/>
-      <c r="B29" s="124"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="124"/>
+      <c r="A29" s="128"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
@@ -5881,6 +5893,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5896,18 +5920,6 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5949,65 +5961,65 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="107" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6536,48 +6548,48 @@
       <c r="L5" s="134"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="130" t="s">
+      <c r="A6" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="130"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="130"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
@@ -6589,17 +6601,17 @@
       <c r="C9" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="132" t="s">
+      <c r="D9" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
@@ -6610,15 +6622,15 @@
         <f>'Cash Flows Statement - indirect'!E46</f>
         <v>0</v>
       </c>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
@@ -6629,15 +6641,15 @@
         <f>'Cash Flows Statement - indirect'!E40</f>
         <v>0</v>
       </c>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
@@ -6648,15 +6660,15 @@
         <f>'Cash Flows Statement - indirect'!E44</f>
         <v>0</v>
       </c>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
@@ -6703,17 +6715,17 @@
       <c r="C15" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6721,15 +6733,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="131"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6737,15 +6749,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="131"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6753,15 +6765,15 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="131"/>
-      <c r="L18" s="131"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
@@ -6808,17 +6820,17 @@
       <c r="C21" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D21" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6826,15 +6838,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6842,15 +6854,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="131"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="131"/>
-      <c r="L23" s="131"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6858,15 +6870,15 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
-      <c r="L24" s="131"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="130"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="130"/>
+      <c r="L24" s="130"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
@@ -6913,17 +6925,17 @@
       <c r="C27" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="132" t="s">
+      <c r="D27" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6931,15 +6943,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="131"/>
-      <c r="L28" s="131"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
+      <c r="L28" s="130"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6947,15 +6959,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
-      <c r="L29" s="131"/>
+      <c r="D29" s="130"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="130"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6963,15 +6975,15 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="131"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="130"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
@@ -7018,17 +7030,17 @@
       <c r="C33" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="132" t="s">
+      <c r="D33" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="132"/>
-      <c r="L33" s="132"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
+      <c r="J33" s="131"/>
+      <c r="K33" s="131"/>
+      <c r="L33" s="131"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -7036,15 +7048,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="131"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
-      <c r="J34" s="131"/>
-      <c r="K34" s="131"/>
-      <c r="L34" s="131"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
+      <c r="J34" s="130"/>
+      <c r="K34" s="130"/>
+      <c r="L34" s="130"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -7052,15 +7064,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="131"/>
-      <c r="E35" s="131"/>
-      <c r="F35" s="131"/>
-      <c r="G35" s="131"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="131"/>
-      <c r="J35" s="131"/>
-      <c r="K35" s="131"/>
-      <c r="L35" s="131"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="130"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="130"/>
+      <c r="L35" s="130"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -7068,15 +7080,15 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="131"/>
-      <c r="E36" s="131"/>
-      <c r="F36" s="131"/>
-      <c r="G36" s="131"/>
-      <c r="H36" s="131"/>
-      <c r="I36" s="131"/>
-      <c r="J36" s="131"/>
-      <c r="K36" s="131"/>
-      <c r="L36" s="131"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="130"/>
+      <c r="K36" s="130"/>
+      <c r="L36" s="130"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
@@ -7123,17 +7135,17 @@
       <c r="C39" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="132" t="s">
+      <c r="D39" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="132"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="131"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="131"/>
+      <c r="J39" s="131"/>
+      <c r="K39" s="131"/>
+      <c r="L39" s="131"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -7141,15 +7153,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="131"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="131"/>
-      <c r="I40" s="131"/>
-      <c r="J40" s="131"/>
-      <c r="K40" s="131"/>
-      <c r="L40" s="131"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="130"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="130"/>
+      <c r="H40" s="130"/>
+      <c r="I40" s="130"/>
+      <c r="J40" s="130"/>
+      <c r="K40" s="130"/>
+      <c r="L40" s="130"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -7157,15 +7169,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="131"/>
-      <c r="J41" s="131"/>
-      <c r="K41" s="131"/>
-      <c r="L41" s="131"/>
+      <c r="D41" s="130"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="130"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="130"/>
+      <c r="J41" s="130"/>
+      <c r="K41" s="130"/>
+      <c r="L41" s="130"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -7173,15 +7185,15 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="131"/>
-      <c r="H42" s="131"/>
-      <c r="I42" s="131"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="131"/>
-      <c r="L42" s="131"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="130"/>
+      <c r="G42" s="130"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="130"/>
+      <c r="J42" s="130"/>
+      <c r="K42" s="130"/>
+      <c r="L42" s="130"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
@@ -7194,18 +7206,33 @@
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="135"/>
-      <c r="E43" s="135"/>
-      <c r="F43" s="135"/>
-      <c r="G43" s="135"/>
-      <c r="H43" s="135"/>
-      <c r="I43" s="135"/>
-      <c r="J43" s="135"/>
-      <c r="K43" s="135"/>
-      <c r="L43" s="135"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="132"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="132"/>
+      <c r="L43" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="D33:L33"/>
@@ -7222,21 +7249,6 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
@@ -7252,7 +7264,7 @@
     <tabColor rgb="FF2F75B5"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -7262,12 +7274,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="105" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="138" t="s">
@@ -7289,7 +7301,7 @@
       <c r="A5" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="108" t="str">
+      <c r="B5" s="107" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
@@ -7336,12 +7348,12 @@
       <c r="D8" s="137"/>
     </row>
     <row r="10" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="122" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="123"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
     </row>
     <row r="11" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
@@ -7418,12 +7430,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="123" t="s">
+      <c r="A18" s="122" t="s">
         <v>305</v>
       </c>
-      <c r="B18" s="123"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
     </row>
     <row r="19" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
@@ -7486,12 +7498,12 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="123" t="s">
+      <c r="A25" s="122" t="s">
         <v>321</v>
       </c>
-      <c r="B25" s="123"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
     </row>
     <row r="26" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
@@ -7506,101 +7518,113 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="38" t="s">
-        <v>325</v>
+      <c r="A27" s="139" t="s">
+        <v>350</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="12" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="12" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="12" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="38" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="38" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C31" s="24"/>
       <c r="D31" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="12" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="123" t="s">
+    <row r="34" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="122" t="s">
         <v>340</v>
       </c>
-      <c r="B33" s="123"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-    </row>
-    <row r="34" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="136" t="s">
+      <c r="B34" s="122"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="122"/>
+    </row>
+    <row r="35" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="136" t="s">
         <v>341</v>
-      </c>
-      <c r="B34" s="137"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-    </row>
-    <row r="35" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="136" t="s">
-        <v>342</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
       <c r="D35" s="137"/>
+    </row>
+    <row r="36" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="136" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" s="137"/>
+      <c r="C36" s="137"/>
+      <c r="D36" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/noprofit/en/11255/inpas-template.xlsx
+++ b/noprofit/en/11255/inpas-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE7DD58-AD2F-4706-809F-E50895CADAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EDFB9-0844-412D-84BD-BAD086376BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
@@ -1102,13 +1102,13 @@
     <t>[+/-] Restricted Fund C</t>
   </si>
   <si>
-    <t>Disclose fundraising costs by category, including direct, shared and support costs where applicable. Explain the methods used to allocate and apportion these costs, and disclose the information required for activities serving more than one purpose.</t>
-  </si>
-  <si>
     <t>Fundraising costs</t>
   </si>
   <si>
     <t>D3</t>
+  </si>
+  <si>
+    <t>Disclose fundraising costs by category, including direct, shared and support costs where applicable. Explain the methods used to allocate and apportion these costs, and disclose the information required for activities serving more than one purpose. Present fundraising costs on a gross basis. Do not deduct them from the related income. For immaterial fundraising categories, provide the required narrative description.</t>
   </si>
 </sst>
 </file>
@@ -1595,6 +1595,9 @@
     <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1604,6 +1607,18 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1613,18 +1628,6 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1649,47 +1652,47 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1697,9 +1700,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2090,333 +2090,327 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="106" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="104">
+      <c r="B8" s="105">
         <v>45292</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="104">
+      <c r="B9" s="105">
         <v>45657</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="105" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="96"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="96"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="105" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="105" t="s">
         <v>240</v>
       </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="105" t="s">
         <v>232</v>
       </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
-      <c r="B26" s="104" t="s">
+      <c r="B26" s="105" t="s">
         <v>243</v>
       </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
-      <c r="B27" s="104" t="s">
+      <c r="B27" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
-      <c r="B28" s="104" t="s">
+      <c r="B28" s="105" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2433,6 +2427,12 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2461,84 +2461,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="107" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>241</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -2561,12 +2561,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -2661,12 +2661,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="113" t="s">
+      <c r="B17" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
@@ -2794,12 +2794,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="113" t="s">
+      <c r="B26" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
@@ -2927,12 +2927,12 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="113" t="s">
+      <c r="B35" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="113"/>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
@@ -3009,12 +3009,12 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="113"/>
-      <c r="E41" s="113"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="113" t="s">
+      <c r="B49" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="113"/>
+      <c r="C49" s="111"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="113" t="s">
+      <c r="B50" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="113"/>
+      <c r="C50" s="111"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -3183,11 +3183,11 @@
       <c r="A53" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="112" t="str">
+      <c r="B53" s="110" t="str">
         <f>IF(ABS(D53)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="112"/>
+      <c r="C53" s="110"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -3197,12 +3197,12 @@
       <c r="A54" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="111" t="str">
+      <c r="B54" s="109" t="str">
         <f>IF(ABS(E54)&lt;0.01,"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="111"/>
-      <c r="D54" s="111"/>
+      <c r="C54" s="109"/>
+      <c r="D54" s="109"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -3216,6 +3216,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B53:C53"/>
@@ -3226,11 +3231,6 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B53">
@@ -3284,13 +3284,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
@@ -3298,72 +3298,72 @@
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="115" t="str">
+      <c r="B2" s="116" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="115" t="str">
+      <c r="B3" s="116" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="117">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="117">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3943,13 +3943,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3958,72 +3958,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="107" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -4046,10 +4046,10 @@
       <c r="A10" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="117" t="s">
+      <c r="B10" s="118" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="117"/>
+      <c r="C10" s="118"/>
       <c r="D10" s="14">
         <f>'Statement of Financial Position'!D33</f>
         <v>0</v>
@@ -4084,11 +4084,11 @@
       <c r="A13" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="119" t="s">
+      <c r="B13" s="120" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="119"/>
-      <c r="D13" s="119"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="14">
         <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
@@ -4098,22 +4098,22 @@
       <c r="A14" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="120" t="s">
         <v>251</v>
       </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
       <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
-      <c r="B15" s="118" t="s">
+      <c r="B15" s="119" t="s">
         <v>252</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
       <c r="E15" s="67">
         <f>SUM(E13:E14)</f>
         <v>0</v>
@@ -4147,11 +4147,11 @@
       <c r="A18" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="120" t="s">
+      <c r="B18" s="121" t="s">
         <v>346</v>
       </c>
-      <c r="C18" s="120"/>
-      <c r="D18" s="120"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
       <c r="E18" s="14">
         <v>0</v>
       </c>
@@ -4160,11 +4160,11 @@
       <c r="A19" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="B19" s="120" t="s">
+      <c r="B19" s="121" t="s">
         <v>347</v>
       </c>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
       <c r="E19" s="14">
         <v>0</v>
       </c>
@@ -4173,11 +4173,11 @@
       <c r="A20" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="121" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="121"/>
       <c r="E20" s="14">
         <v>0</v>
       </c>
@@ -4186,11 +4186,11 @@
       <c r="A21" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B21" s="120" t="s">
+      <c r="B21" s="121" t="s">
         <v>219</v>
       </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
       <c r="E21" s="14">
         <v>0</v>
       </c>
@@ -4199,22 +4199,22 @@
       <c r="A22" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="120" t="s">
         <v>220</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
       <c r="E22" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="119" t="s">
         <v>254</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
       <c r="E23" s="67">
         <f>SUM(E18:E22)</f>
         <v>0</v>
@@ -4232,11 +4232,11 @@
       <c r="A25" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="118" t="s">
+      <c r="B25" s="119" t="s">
         <v>234</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
       <c r="E25" s="62">
         <f>SUM(D10,E15,E23)</f>
         <v>0</v>
@@ -4244,6 +4244,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B25:D25"/>
@@ -4256,11 +4261,6 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4287,94 +4287,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="107" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="124" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="124"/>
       <c r="D9" s="74" t="s">
         <v>27</v>
       </c>
@@ -4387,31 +4387,31 @@
       <c r="A10" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="111" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
       <c r="E10" s="22">
         <f>'Statement of Income &amp; Expenses'!E41</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="122"/>
+      <c r="C12" s="124"/>
       <c r="D12" s="74" t="s">
         <v>27</v>
       </c>
@@ -4424,10 +4424,10 @@
       <c r="A13" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="121" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="120"/>
+      <c r="C13" s="121"/>
       <c r="D13" s="90"/>
       <c r="E13" s="22">
         <v>0</v>
@@ -4437,10 +4437,10 @@
       <c r="A14" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="121" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="120"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="90"/>
       <c r="E14" s="22">
         <v>0</v>
@@ -4450,10 +4450,10 @@
       <c r="A15" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="120" t="s">
+      <c r="B15" s="121" t="s">
         <v>257</v>
       </c>
-      <c r="C15" s="120"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="90"/>
       <c r="E15" s="22">
         <v>0</v>
@@ -4463,10 +4463,10 @@
       <c r="A16" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="120" t="s">
+      <c r="B16" s="121" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="120"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="90"/>
       <c r="E16" s="22">
         <v>0</v>
@@ -4477,10 +4477,10 @@
       <c r="A17" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="120" t="s">
+      <c r="B17" s="121" t="s">
         <v>259</v>
       </c>
-      <c r="C17" s="120"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="90"/>
       <c r="E17" s="22">
         <v>0</v>
@@ -4491,10 +4491,10 @@
       <c r="A18" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="B18" s="120" t="s">
+      <c r="B18" s="121" t="s">
         <v>260</v>
       </c>
-      <c r="C18" s="120"/>
+      <c r="C18" s="121"/>
       <c r="D18" s="90"/>
       <c r="E18" s="22">
         <v>0</v>
@@ -4505,10 +4505,10 @@
       <c r="A19" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="120" t="s">
+      <c r="B19" s="121" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="120"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="90"/>
       <c r="E19" s="22">
         <v>0</v>
@@ -4519,10 +4519,10 @@
       <c r="A20" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="121" t="s">
         <v>222</v>
       </c>
-      <c r="C20" s="120"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="90"/>
       <c r="E20" s="22">
         <v>0</v>
@@ -4587,11 +4587,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="113" t="s">
+      <c r="B25" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="113"/>
-      <c r="D25" s="113"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4608,10 +4608,10 @@
       <c r="A27" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="122" t="s">
+      <c r="B27" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="122"/>
+      <c r="C27" s="124"/>
       <c r="D27" s="74" t="s">
         <v>27</v>
       </c>
@@ -4674,11 +4674,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="113" t="s">
+      <c r="B32" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="113"/>
-      <c r="D32" s="113"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
       <c r="E32" s="62">
         <f>SUM(E28:E31)</f>
         <v>0</v>
@@ -4695,10 +4695,10 @@
       <c r="A34" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="124" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="122"/>
+      <c r="C34" s="124"/>
       <c r="D34" s="74" t="s">
         <v>27</v>
       </c>
@@ -4749,11 +4749,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="113" t="s">
+      <c r="B38" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
       <c r="E38" s="62">
         <f>SUM(E35:E37)</f>
         <v>0</v>
@@ -4768,11 +4768,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="113" t="s">
+      <c r="B40" s="111" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4789,10 +4789,10 @@
       <c r="A42" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="121" t="s">
+      <c r="B42" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="C42" s="121"/>
+      <c r="C42" s="122"/>
       <c r="D42" s="26"/>
       <c r="E42" s="22">
         <f>E46</f>
@@ -4803,10 +4803,10 @@
       <c r="A43" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="B43" s="121" t="s">
+      <c r="B43" s="122" t="s">
         <v>263</v>
       </c>
-      <c r="C43" s="121"/>
+      <c r="C43" s="122"/>
       <c r="D43" s="26"/>
       <c r="E43" s="22">
         <f>E40</f>
@@ -4817,10 +4817,10 @@
       <c r="A44" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="B44" s="121" t="s">
+      <c r="B44" s="122" t="s">
         <v>185</v>
       </c>
-      <c r="C44" s="121"/>
+      <c r="C44" s="122"/>
       <c r="D44" s="26"/>
       <c r="E44" s="22">
         <v>0</v>
@@ -4828,10 +4828,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="113" t="s">
+      <c r="B45" s="111" t="s">
         <v>264</v>
       </c>
-      <c r="C45" s="113"/>
+      <c r="C45" s="111"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4842,11 +4842,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="113" t="s">
+      <c r="B46" s="111" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="113"/>
-      <c r="D46" s="113"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
       <c r="E46" s="69">
         <f>SUM('Statement of Financial Position'!D18:D19)</f>
         <v>0</v>
@@ -4854,11 +4854,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="113" t="s">
+      <c r="B47" s="111" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="113"/>
-      <c r="D47" s="113"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
       <c r="E47" s="69">
         <f>SUM('Statement of Financial Position'!E18:E19)</f>
         <v>0</v>
@@ -4866,11 +4866,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="113" t="s">
+      <c r="B48" s="111" t="s">
         <v>265</v>
       </c>
-      <c r="C48" s="113"/>
-      <c r="D48" s="113"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
       <c r="E48" s="69">
         <f>E45-E47</f>
         <v>0</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="121" t="s">
+      <c r="B52" s="122" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="121"/>
+      <c r="C52" s="122"/>
       <c r="D52" s="90">
         <v>50</v>
       </c>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="121" t="s">
+      <c r="B53" s="122" t="s">
         <v>118</v>
       </c>
-      <c r="C53" s="121"/>
+      <c r="C53" s="122"/>
       <c r="D53" s="90">
         <v>51</v>
       </c>
@@ -4923,10 +4923,10 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="121" t="s">
+      <c r="B54" s="122" t="s">
         <v>235</v>
       </c>
-      <c r="C54" s="121"/>
+      <c r="C54" s="122"/>
       <c r="D54" s="90">
         <v>52</v>
       </c>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
-      <c r="B55" s="121" t="s">
+      <c r="B55" s="122" t="s">
         <v>236</v>
       </c>
-      <c r="C55" s="121"/>
+      <c r="C55" s="122"/>
       <c r="D55" s="90">
         <v>53</v>
       </c>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
-      <c r="B56" s="121" t="s">
+      <c r="B56" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="121"/>
+      <c r="C56" s="122"/>
       <c r="D56" s="90">
         <v>54</v>
       </c>
@@ -4970,18 +4970,25 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4998,25 +5005,18 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -5042,103 +5042,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="107" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="129" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="125"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="127"/>
@@ -5171,76 +5171,76 @@
       <c r="D17" s="127"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="125"/>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
+      <c r="A18" s="126"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="125"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
+      <c r="A19" s="126"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="125"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
+      <c r="A20" s="126"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="125"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
+      <c r="A21" s="126"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="125"/>
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
+      <c r="A22" s="126"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="125"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
+      <c r="A23" s="126"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="125"/>
-      <c r="B24" s="125"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
+      <c r="A24" s="126"/>
+      <c r="B24" s="126"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="126"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="125"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
+      <c r="A25" s="126"/>
+      <c r="B25" s="126"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="125"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="126"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="126"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="125"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="125"/>
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="126"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="126"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="128"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
@@ -5893,18 +5893,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5920,6 +5908,18 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5949,77 +5949,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="107" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6456,140 +6456,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="133" t="str">
+      <c r="B2" s="134" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="133" t="str">
+      <c r="B3" s="134" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="134">
+      <c r="B4" s="135">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="134">
+      <c r="B5" s="135">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="131" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
+      <c r="B6" s="131"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="131"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="131"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="135"/>
-      <c r="B7" s="135"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="135"/>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
+      <c r="A8" s="131"/>
+      <c r="B8" s="131"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
@@ -6601,17 +6601,17 @@
       <c r="C9" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="131" t="s">
+      <c r="D9" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
@@ -6622,15 +6622,15 @@
         <f>'Cash Flows Statement - indirect'!E46</f>
         <v>0</v>
       </c>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="132"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
@@ -6641,15 +6641,15 @@
         <f>'Cash Flows Statement - indirect'!E40</f>
         <v>0</v>
       </c>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
@@ -6660,15 +6660,15 @@
         <f>'Cash Flows Statement - indirect'!E44</f>
         <v>0</v>
       </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
@@ -6715,17 +6715,17 @@
       <c r="C15" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="131" t="s">
+      <c r="D15" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6733,15 +6733,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6749,15 +6749,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6765,15 +6765,15 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
@@ -6820,17 +6820,17 @@
       <c r="C21" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6838,15 +6838,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6854,15 +6854,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="130"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="130"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="132"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6870,15 +6870,15 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="130"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="130"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="132"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
@@ -6925,17 +6925,17 @@
       <c r="C27" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="131" t="s">
+      <c r="D27" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="131"/>
-      <c r="L27" s="131"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6943,15 +6943,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
-      <c r="L28" s="130"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="132"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6959,15 +6959,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="130"/>
-      <c r="K29" s="130"/>
-      <c r="L29" s="130"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="132"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6975,15 +6975,15 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="130"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="132"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="132"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
@@ -7030,17 +7030,17 @@
       <c r="C33" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="131" t="s">
+      <c r="D33" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="131"/>
-      <c r="F33" s="131"/>
-      <c r="G33" s="131"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="131"/>
-      <c r="J33" s="131"/>
-      <c r="K33" s="131"/>
-      <c r="L33" s="131"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -7048,15 +7048,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="130"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="130"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="130"/>
-      <c r="I34" s="130"/>
-      <c r="J34" s="130"/>
-      <c r="K34" s="130"/>
-      <c r="L34" s="130"/>
+      <c r="D34" s="132"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="132"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="132"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -7064,15 +7064,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="130"/>
-      <c r="E35" s="130"/>
-      <c r="F35" s="130"/>
-      <c r="G35" s="130"/>
-      <c r="H35" s="130"/>
-      <c r="I35" s="130"/>
-      <c r="J35" s="130"/>
-      <c r="K35" s="130"/>
-      <c r="L35" s="130"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="132"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -7080,15 +7080,15 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="130"/>
-      <c r="G36" s="130"/>
-      <c r="H36" s="130"/>
-      <c r="I36" s="130"/>
-      <c r="J36" s="130"/>
-      <c r="K36" s="130"/>
-      <c r="L36" s="130"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="132"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="132"/>
+      <c r="J36" s="132"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="132"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
@@ -7135,17 +7135,17 @@
       <c r="C39" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="131" t="s">
+      <c r="D39" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="131"/>
-      <c r="J39" s="131"/>
-      <c r="K39" s="131"/>
-      <c r="L39" s="131"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -7153,15 +7153,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="130"/>
-      <c r="E40" s="130"/>
-      <c r="F40" s="130"/>
-      <c r="G40" s="130"/>
-      <c r="H40" s="130"/>
-      <c r="I40" s="130"/>
-      <c r="J40" s="130"/>
-      <c r="K40" s="130"/>
-      <c r="L40" s="130"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="132"/>
+      <c r="H40" s="132"/>
+      <c r="I40" s="132"/>
+      <c r="J40" s="132"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="132"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -7169,15 +7169,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="130"/>
-      <c r="E41" s="130"/>
-      <c r="F41" s="130"/>
-      <c r="G41" s="130"/>
-      <c r="H41" s="130"/>
-      <c r="I41" s="130"/>
-      <c r="J41" s="130"/>
-      <c r="K41" s="130"/>
-      <c r="L41" s="130"/>
+      <c r="D41" s="132"/>
+      <c r="E41" s="132"/>
+      <c r="F41" s="132"/>
+      <c r="G41" s="132"/>
+      <c r="H41" s="132"/>
+      <c r="I41" s="132"/>
+      <c r="J41" s="132"/>
+      <c r="K41" s="132"/>
+      <c r="L41" s="132"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -7185,15 +7185,15 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="130"/>
-      <c r="E42" s="130"/>
-      <c r="F42" s="130"/>
-      <c r="G42" s="130"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="130"/>
-      <c r="K42" s="130"/>
-      <c r="L42" s="130"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="132"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
@@ -7206,33 +7206,18 @@
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="132"/>
-      <c r="L43" s="132"/>
+      <c r="D43" s="136"/>
+      <c r="E43" s="136"/>
+      <c r="F43" s="136"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="136"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D15:L15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="D33:L33"/>
@@ -7249,6 +7234,21 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
@@ -7274,38 +7274,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="106" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="139" t="s">
         <v>277</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
     </row>
     <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="137" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
     </row>
     <row r="5" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="107" t="str">
+      <c r="B5" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C5" s="137"/>
+      <c r="C5" s="138"/>
       <c r="D5" s="12" t="s">
         <v>280</v>
       </c>
@@ -7340,20 +7340,20 @@
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="137" t="s">
         <v>284</v>
       </c>
-      <c r="B8" s="137"/>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
     </row>
     <row r="10" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="122" t="s">
+      <c r="A10" s="124" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
     </row>
     <row r="11" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
@@ -7430,12 +7430,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="124" t="s">
         <v>305</v>
       </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
     </row>
     <row r="19" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
@@ -7498,12 +7498,12 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="122" t="s">
+      <c r="A25" s="124" t="s">
         <v>321</v>
       </c>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
     </row>
     <row r="26" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
@@ -7518,15 +7518,15 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="139" t="s">
-        <v>350</v>
+      <c r="A27" s="104" t="s">
+        <v>349</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
@@ -7590,28 +7590,28 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="122" t="s">
+      <c r="A34" s="124" t="s">
         <v>340</v>
       </c>
-      <c r="B34" s="122"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
     </row>
     <row r="35" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="136" t="s">
+      <c r="A35" s="137" t="s">
         <v>341</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
+      <c r="B35" s="138"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
     </row>
     <row r="36" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="136" t="s">
+      <c r="A36" s="137" t="s">
         <v>342</v>
       </c>
-      <c r="B36" s="137"/>
-      <c r="C36" s="137"/>
-      <c r="D36" s="137"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="11">
